--- a/src/app/api/FeedExistingData/26-27_online_data.xlsx
+++ b/src/app/api/FeedExistingData/26-27_online_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f13febc4eefe037/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{CE6CC82B-F9E9-4752-9B51-396A2671DD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F149841-723E-4896-A4D7-697067AE90CD}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{CE6CC82B-F9E9-4752-9B51-396A2671DD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6B3B5D-912B-4CD1-BFD4-E9FCBF036D59}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4F84B448-CAD8-4F99-8C80-2C3971096148}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="386">
   <si>
     <t>VAMSHI KRISHNA</t>
   </si>
@@ -72,69 +72,9 @@
     <t>8688270401`</t>
   </si>
   <si>
-    <t>R MUTHULINGAM</t>
-  </si>
-  <si>
-    <t>MERUGU HARI</t>
-  </si>
-  <si>
-    <t>CH MADHUGOPAL</t>
-  </si>
-  <si>
-    <t>J SUNIL KUMAR</t>
-  </si>
-  <si>
-    <t>MITHRA DASAHRI</t>
-  </si>
-  <si>
-    <t>A SHAVAN</t>
-  </si>
-  <si>
-    <t>D RAKESH CHANDRA</t>
-  </si>
-  <si>
-    <t>K RAVI KUMAR</t>
-  </si>
-  <si>
-    <t>SUDHAKAR KOMMU</t>
-  </si>
-  <si>
-    <t>JEEVAN KUMAR</t>
-  </si>
-  <si>
-    <t>RAMA AIKYA</t>
-  </si>
-  <si>
-    <t>VIGNESHARYAN</t>
-  </si>
-  <si>
-    <t>KALYAN KUMAR</t>
-  </si>
-  <si>
     <t>Y RAJAMOULI</t>
   </si>
   <si>
-    <t>K ARUN KUMAR</t>
-  </si>
-  <si>
-    <t>KUHAN REKHA THOTA</t>
-  </si>
-  <si>
-    <t>THUMMA NAVEEN KUMAR</t>
-  </si>
-  <si>
-    <t>SRINIVAS BADAVATH</t>
-  </si>
-  <si>
-    <t>G SRINIVAS</t>
-  </si>
-  <si>
-    <t>ANDAL SRIDHAR KOTANCHA</t>
-  </si>
-  <si>
-    <t>K SAI TEJ</t>
-  </si>
-  <si>
     <t>VIJAYA NAGINA</t>
   </si>
   <si>
@@ -693,73 +633,16 @@
     <t>T NANDINI</t>
   </si>
   <si>
-    <t>NWZPS8914K</t>
-  </si>
-  <si>
     <t>AHJPK94782</t>
   </si>
   <si>
     <t>AHDPC68774</t>
   </si>
   <si>
-    <t>H.NO. 2-4-1525, ASHKOK COLONY, ROAD 10A, NEAR SUMANGALI HALL, HANAMAKONDA 506001</t>
-  </si>
-  <si>
-    <t>H.NO. 6-4-91, BRAHMANAWADA, HANAMAKONDA, WARANGAL 506003</t>
-  </si>
-  <si>
     <t>H.NO. 11-95-167/1, KOTHAWADA, WARANGAL 506002</t>
   </si>
   <si>
-    <t>H.NO. 3-4-415/1, RAYAPOOR, HANAMAKONDA 506001</t>
-  </si>
-  <si>
-    <t>H.NO. 18-4-178, KAMANPUR, KAREEMABAD, WARANGAL 506002</t>
-  </si>
-  <si>
-    <t>H.NO. 30-4-54, OPP ZPHS SCHOOL, MADIKONDA, KAZIPET, HANAMAKONDA 506142</t>
-  </si>
-  <si>
-    <t>H.NO 9-8-67, ELLAM BAZAR, WARANGAL 506002</t>
-  </si>
-  <si>
-    <t>FLAT NO 307, GAK HILL RIDGE APARTMENT, HUNTER ROAD, OPP LANE TO BLUEMOON HOTEL, SHYAMPET 506001</t>
-  </si>
-  <si>
-    <t>H.NO. 5-4/6, SAI GANESH COLONY, KASHIBUGGA, WARANGAL 506002</t>
-  </si>
-  <si>
-    <t>H.NO. 11-18- 231, TSNPDCL LANE SOCIETY COLONY, KASIBUGGA, WARANGAL 506002</t>
-  </si>
-  <si>
-    <t>H.NO. 2-83, SEETHARAMPURAM, HANAMAKONDA 506342</t>
-  </si>
-  <si>
-    <t>H.NO. 12-7-174, RAMANNAPET, BATTALABAZAR, WARANGLA 506002</t>
-  </si>
-  <si>
     <t>H.NO. 2-5-25, RAMANAGAR, HANAMAKONDA 506001</t>
-  </si>
-  <si>
-    <t>H.NO. 3-14-174, YADAV NAGAR, HANAMAKONDA 506001</t>
-  </si>
-  <si>
-    <t>H.NO. 6-147, SUSHILIA, HYDERABAD 500065</t>
-  </si>
-  <si>
-    <t>H.NO. 1-22, KUMARIKUNTA, PEDDAPALLI, KARIMNAGAR 505525</t>
-  </si>
-  <si>
-    <t>SURYANAYAK THANDA, SHYAMPET, HANAMAKONDA 506164</t>
-  </si>
-  <si>
-    <t>H.NO. 3-14-452, REDDY COLONY, NEAR VIKAS MASTERJI SCHOOL, HANAMAKONDA 506001</t>
-  </si>
-  <si>
-    <t>NEAR NARASIMHA SWAMY TEMPLE 506348</t>
-  </si>
-  <si>
-    <t>SUBEDARI, HANAMAKONDA</t>
   </si>
   <si>
     <t>H.NO. 5-149, SAI NAGAR STREET, NARSAMPET 506132</t>
@@ -1829,7 +1712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25382976-8DEB-4D0A-8766-3B76A57A6C02}">
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J979"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -1876,1521 +1759,1515 @@
     </row>
     <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>9390003003</v>
+        <v>9966845948</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E2" s="2"/>
       <c r="G2" s="1">
-        <v>1649</v>
+        <v>2239</v>
       </c>
       <c r="H2" s="7">
-        <v>46114</v>
+        <v>46126</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>6302321209</v>
+        <v>9849264112</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
         <v>516</v>
       </c>
       <c r="E3" s="2"/>
       <c r="G3" s="1">
-        <v>1648</v>
+        <v>2234</v>
       </c>
       <c r="H3" s="7">
-        <v>46114</v>
+        <v>46126</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>9394052517</v>
+        <v>9848756833</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>516</v>
       </c>
       <c r="E4" s="2"/>
       <c r="G4" s="1">
-        <v>1647</v>
+        <v>2235</v>
       </c>
       <c r="H4" s="7">
-        <v>46114</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>224</v>
+        <v>46126</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>8686858643</v>
+        <v>9502176065</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>516</v>
+        <v>2116</v>
       </c>
       <c r="E5" s="2"/>
       <c r="G5" s="1">
-        <v>2203</v>
+        <v>2236</v>
       </c>
       <c r="H5" s="7">
-        <v>46115</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>225</v>
+        <v>46126</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>8686858643</v>
+        <v>8688368382</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>1500</v>
+        <v>516</v>
       </c>
       <c r="E6" s="2"/>
       <c r="G6" s="1">
-        <v>2202</v>
+        <v>2237</v>
       </c>
       <c r="H6" s="7">
-        <v>46115</v>
+        <v>46126</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>9502382033</v>
+        <v>9177320518</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="G7" s="1">
-        <v>2204</v>
+        <v>1628</v>
       </c>
       <c r="H7" s="7">
-        <v>46115</v>
+        <v>46127</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>9908539270</v>
+        <v>9145398278</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E8" s="2"/>
       <c r="G8" s="1">
-        <v>2206</v>
+        <v>2241</v>
       </c>
       <c r="H8" s="7">
-        <v>46115</v>
+        <v>46127</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>9908114977</v>
+        <v>8074189232</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1">
         <v>516</v>
       </c>
       <c r="E9" s="2"/>
       <c r="G9" s="1">
-        <v>1650</v>
+        <v>2244</v>
       </c>
       <c r="H9" s="7">
-        <v>46115</v>
+        <v>46128</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>8096375340</v>
+        <v>9502216786</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E10" s="2"/>
       <c r="G10" s="1">
-        <v>2211</v>
+        <v>2245</v>
       </c>
       <c r="H10" s="7">
-        <v>46117</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>229</v>
+        <v>46128</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>9700949460</v>
+        <v>9550474521</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
-        <v>10116</v>
+        <v>1116</v>
       </c>
       <c r="E11" s="2"/>
       <c r="G11" s="1">
-        <v>2213</v>
+        <v>2249</v>
       </c>
       <c r="H11" s="7">
-        <v>46117</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>230</v>
+        <v>46130</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>9948193728</v>
+        <v>6281472173</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1">
-        <v>516</v>
+        <v>3116</v>
       </c>
       <c r="E12" s="2"/>
       <c r="G12" s="1">
-        <v>2212</v>
+        <v>2246</v>
       </c>
       <c r="H12" s="7">
-        <v>46117</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>231</v>
+        <v>46130</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>9491194290</v>
+        <v>6281472173</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="1">
-        <v>516</v>
+        <v>116</v>
       </c>
       <c r="E13" s="2"/>
       <c r="G13" s="1">
-        <v>2215</v>
+        <v>2247</v>
       </c>
       <c r="H13" s="7">
-        <v>46118</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>232</v>
+        <v>46130</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>9849311537</v>
+        <v>6281472173</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E14" s="2"/>
       <c r="G14" s="1">
-        <v>2216</v>
+        <v>2248</v>
       </c>
       <c r="H14" s="7">
-        <v>46119</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>233</v>
+        <v>46130</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>9000166687</v>
+        <v>8143235383</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="1">
-        <v>2000</v>
+        <v>216</v>
       </c>
       <c r="E15" s="2"/>
       <c r="G15" s="1">
-        <v>2221</v>
+        <v>2615</v>
       </c>
       <c r="H15" s="7">
-        <v>46119</v>
+        <v>46131</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>9700779166</v>
+        <v>8143235383</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16" s="1">
-        <v>516</v>
+        <v>1016</v>
       </c>
       <c r="E16" s="2"/>
       <c r="G16" s="1">
-        <v>2219</v>
+        <v>2614</v>
       </c>
       <c r="H16" s="7">
-        <v>46120</v>
+        <v>46131</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>9963378931</v>
+        <v>9177998395</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" s="1">
         <v>516</v>
       </c>
       <c r="E17" s="2"/>
       <c r="G17" s="1">
-        <v>2222</v>
+        <v>2613</v>
       </c>
       <c r="H17" s="7">
-        <v>46121</v>
+        <v>46131</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>9000833173</v>
+        <v>9440120755</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E18" s="2"/>
       <c r="G18" s="1">
-        <v>2223</v>
+        <v>2611</v>
       </c>
       <c r="H18" s="7">
-        <v>46122</v>
+        <v>46131</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>7013036702</v>
+        <v>8074746174</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1">
-        <v>20000</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>219</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="E19" s="2"/>
       <c r="G19" s="1">
-        <v>2226</v>
+        <v>2610</v>
       </c>
       <c r="H19" s="7">
-        <v>46124</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>238</v>
+        <v>46131</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>9963793774</v>
+        <v>9177002339</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1">
         <v>516</v>
       </c>
       <c r="E20" s="2"/>
       <c r="G20" s="1">
-        <v>2227</v>
+        <v>2601</v>
       </c>
       <c r="H20" s="7">
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>7702459658</v>
+        <v>9885478447</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1">
-        <v>5016</v>
+        <v>1116</v>
       </c>
       <c r="E21" s="2"/>
       <c r="G21" s="1">
-        <v>2228</v>
+        <v>2602</v>
       </c>
       <c r="H21" s="7">
-        <v>46124</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>240</v>
+        <v>46131</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>7993717797</v>
+        <v>9014785706</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1">
-        <v>2500</v>
+        <v>516</v>
       </c>
       <c r="E22" s="2"/>
       <c r="G22" s="1">
-        <v>2231</v>
+        <v>2603</v>
       </c>
       <c r="H22" s="7">
-        <v>46125</v>
+        <v>46131</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>9966845948</v>
+        <v>8297369701</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C23" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E23" s="2"/>
       <c r="G23" s="1">
-        <v>2239</v>
+        <v>2604</v>
       </c>
       <c r="H23" s="7">
-        <v>46126</v>
+        <v>46131</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>9849264112</v>
+        <v>9704304537</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1">
         <v>516</v>
       </c>
       <c r="E24" s="2"/>
       <c r="G24" s="1">
-        <v>2234</v>
+        <v>2607</v>
       </c>
       <c r="H24" s="7">
-        <v>46126</v>
+        <v>46131</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>9848756833</v>
+        <v>9000586457</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1">
-        <v>516</v>
+        <v>1016</v>
       </c>
       <c r="E25" s="2"/>
       <c r="G25" s="1">
-        <v>2235</v>
+        <v>2635</v>
       </c>
       <c r="H25" s="7">
-        <v>46126</v>
+        <v>46132</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>9502176065</v>
+        <v>8688056550</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1">
-        <v>2116</v>
+        <v>516</v>
       </c>
       <c r="E26" s="2"/>
       <c r="G26" s="1">
-        <v>2236</v>
+        <v>2634</v>
       </c>
       <c r="H26" s="7">
-        <v>46126</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>245</v>
+        <v>46132</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>8688368382</v>
+        <v>7416646166</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E27" s="2"/>
       <c r="G27" s="1">
-        <v>2237</v>
+        <v>2626</v>
       </c>
       <c r="H27" s="7">
-        <v>46126</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>246</v>
+        <v>46132</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>9177320518</v>
+        <v>9652544683</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E28" s="2"/>
       <c r="G28" s="1">
-        <v>1628</v>
+        <v>2624</v>
       </c>
       <c r="H28" s="7">
-        <v>46127</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>247</v>
+        <v>46132</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
-        <v>9145398278</v>
+        <v>9000249197</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29" s="1">
-        <v>1116</v>
+        <v>1016</v>
       </c>
       <c r="E29" s="2"/>
       <c r="G29" s="1">
-        <v>2241</v>
+        <v>2623</v>
       </c>
       <c r="H29" s="7">
-        <v>46127</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>248</v>
+        <v>46132</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
-        <v>8074189232</v>
+        <v>6305229119</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="E30" s="2"/>
       <c r="G30" s="1">
-        <v>2244</v>
+        <v>2622</v>
       </c>
       <c r="H30" s="7">
-        <v>46128</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>249</v>
+        <v>46132</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
-        <v>9502216786</v>
+        <v>6305229119</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1">
-        <v>501</v>
+        <v>1000</v>
       </c>
       <c r="E31" s="2"/>
       <c r="G31" s="1">
-        <v>2245</v>
+        <v>2621</v>
       </c>
       <c r="H31" s="7">
-        <v>46128</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>250</v>
+        <v>46132</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
-        <v>9550474521</v>
+        <v>9502768753</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C32" s="1">
-        <v>1116</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="2"/>
       <c r="G32" s="1">
-        <v>2249</v>
+        <v>2620</v>
       </c>
       <c r="H32" s="7">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
-        <v>6281472173</v>
+        <v>9959606072</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C33" s="1">
-        <v>3116</v>
+        <v>516</v>
       </c>
       <c r="E33" s="2"/>
       <c r="G33" s="1">
-        <v>2246</v>
+        <v>2617</v>
       </c>
       <c r="H33" s="7">
-        <v>46130</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>252</v>
+        <v>46132</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
-        <v>6281472173</v>
+        <v>9177159566</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C34" s="1">
-        <v>116</v>
+        <v>516</v>
       </c>
       <c r="E34" s="2"/>
       <c r="G34" s="1">
-        <v>2247</v>
+        <v>2616</v>
       </c>
       <c r="H34" s="7">
-        <v>46130</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>252</v>
+        <v>46132</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
-        <v>6281472173</v>
+        <v>9441335062</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C35" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E35" s="2"/>
       <c r="G35" s="1">
-        <v>2248</v>
+        <v>2638</v>
       </c>
       <c r="H35" s="7">
-        <v>46130</v>
+        <v>46133</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
-        <v>8143235383</v>
+        <v>8886042342</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C36" s="1">
-        <v>216</v>
+        <v>2104</v>
       </c>
       <c r="E36" s="2"/>
       <c r="G36" s="1">
-        <v>2615</v>
+        <v>2637</v>
       </c>
       <c r="H36" s="7">
-        <v>46131</v>
+        <v>46133</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
-        <v>8143235383</v>
+        <v>9573777269</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="1">
-        <v>1016</v>
+        <v>516</v>
       </c>
       <c r="E37" s="2"/>
       <c r="G37" s="1">
-        <v>2614</v>
+        <v>2636</v>
       </c>
       <c r="H37" s="7">
-        <v>46131</v>
+        <v>46133</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
-        <v>9177998395</v>
+        <v>9440936044</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" s="1">
         <v>516</v>
       </c>
       <c r="E38" s="2"/>
       <c r="G38" s="1">
-        <v>2613</v>
+        <v>2640</v>
       </c>
       <c r="H38" s="7">
-        <v>46131</v>
+        <v>46134</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
-        <v>9440120755</v>
+        <v>9394052517</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="1">
         <v>1116</v>
       </c>
       <c r="E39" s="2"/>
       <c r="G39" s="1">
-        <v>2611</v>
+        <v>2639</v>
       </c>
       <c r="H39" s="7">
-        <v>46131</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>255</v>
+        <v>46134</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
-        <v>8074746174</v>
+        <v>9440581852</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E40" s="2"/>
       <c r="G40" s="1">
-        <v>2610</v>
+        <v>2641</v>
       </c>
       <c r="H40" s="7">
-        <v>46131</v>
+        <v>46135</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
-        <v>9177002339</v>
+        <v>9885500288</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C41" s="1">
-        <v>516</v>
+        <v>6000</v>
       </c>
       <c r="E41" s="2"/>
       <c r="G41" s="1">
-        <v>2601</v>
+        <v>2643</v>
       </c>
       <c r="H41" s="7">
-        <v>46131</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>257</v>
+        <v>46135</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
-        <v>9885478447</v>
+        <v>9440581852</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C42" s="1">
         <v>1116</v>
       </c>
       <c r="E42" s="2"/>
       <c r="G42" s="1">
-        <v>2602</v>
+        <v>2642</v>
       </c>
       <c r="H42" s="7">
-        <v>46131</v>
+        <v>46135</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
-        <v>9014785706</v>
+        <v>9182177515</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C43" s="1">
         <v>516</v>
       </c>
       <c r="E43" s="2"/>
       <c r="G43" s="1">
-        <v>2603</v>
+        <v>2647</v>
       </c>
       <c r="H43" s="7">
-        <v>46131</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>259</v>
+        <v>46136</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
-        <v>8297369701</v>
+        <v>9966086753</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C44" s="1">
         <v>516</v>
       </c>
       <c r="E44" s="2"/>
       <c r="G44" s="1">
-        <v>2604</v>
+        <v>2646</v>
       </c>
       <c r="H44" s="7">
-        <v>46131</v>
+        <v>46136</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
-        <v>9704304537</v>
+        <v>9849453644</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C45" s="1">
         <v>516</v>
       </c>
       <c r="E45" s="2"/>
       <c r="G45" s="1">
-        <v>2607</v>
+        <v>2645</v>
       </c>
       <c r="H45" s="7">
-        <v>46131</v>
+        <v>46136</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
-        <v>9000586457</v>
+        <v>9704353685</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C46" s="1">
-        <v>1016</v>
+        <v>516</v>
       </c>
       <c r="E46" s="2"/>
       <c r="G46" s="1">
-        <v>2635</v>
+        <v>2650</v>
       </c>
       <c r="H46" s="7">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
-        <v>8688056550</v>
+        <v>9000236644</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C47" s="1">
         <v>516</v>
       </c>
       <c r="E47" s="2"/>
       <c r="G47" s="1">
-        <v>2634</v>
+        <v>2653</v>
       </c>
       <c r="H47" s="7">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
-        <v>7416646166</v>
+        <v>8019864314</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C48" s="1">
-        <v>501</v>
+        <v>100</v>
       </c>
       <c r="E48" s="2"/>
       <c r="G48" s="1">
-        <v>2626</v>
+        <v>2652</v>
       </c>
       <c r="H48" s="7">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
-        <v>9652544683</v>
+        <v>8919089789</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C49" s="1">
         <v>516</v>
       </c>
       <c r="E49" s="2"/>
       <c r="G49" s="1">
-        <v>2624</v>
+        <v>2662</v>
       </c>
       <c r="H49" s="7">
-        <v>46132</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>264</v>
+        <v>46138</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
-        <v>9000249197</v>
+        <v>9441281179</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C50" s="1">
-        <v>1016</v>
+        <v>501</v>
       </c>
       <c r="E50" s="2"/>
       <c r="G50" s="1">
-        <v>2623</v>
+        <v>2661</v>
       </c>
       <c r="H50" s="7">
-        <v>46132</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>265</v>
+        <v>46138</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
-        <v>6305229119</v>
+        <v>9000249197</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C51" s="1">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="1">
-        <v>2622</v>
+        <v>2658</v>
       </c>
       <c r="H51" s="7">
-        <v>46132</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>264</v>
+        <v>46138</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
-        <v>6305229119</v>
+        <v>8187828483</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C52" s="1">
-        <v>1000</v>
+        <v>516</v>
       </c>
       <c r="E52" s="2"/>
       <c r="G52" s="1">
-        <v>2621</v>
+        <v>2657</v>
       </c>
       <c r="H52" s="7">
-        <v>46132</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>264</v>
+        <v>46138</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
-        <v>9502768753</v>
+        <v>9032031100</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C53" s="1">
-        <v>1000</v>
+        <v>501</v>
       </c>
       <c r="E53" s="2"/>
       <c r="G53" s="1">
-        <v>2620</v>
+        <v>2656</v>
       </c>
       <c r="H53" s="7">
-        <v>46132</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>264</v>
+        <v>46138</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
-        <v>9959606072</v>
-      </c>
+      <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C54" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E54" s="2"/>
       <c r="G54" s="1">
-        <v>2617</v>
+        <v>2666</v>
       </c>
       <c r="H54" s="7">
-        <v>46132</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>266</v>
+        <v>46139</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
-        <v>9177159566</v>
+        <v>9966555091</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C55" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E55" s="2"/>
       <c r="G55" s="1">
-        <v>2616</v>
+        <v>2667</v>
       </c>
       <c r="H55" s="7">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
-        <v>9441335062</v>
+        <v>9502176065</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C56" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E56" s="2"/>
       <c r="G56" s="1">
-        <v>2638</v>
+        <v>2671</v>
       </c>
       <c r="H56" s="7">
-        <v>46133</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>268</v>
+        <v>46140</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
-        <v>8886042342</v>
+        <v>9652202864</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" s="1">
-        <v>2104</v>
+        <v>501</v>
       </c>
       <c r="E57" s="2"/>
       <c r="G57" s="1">
-        <v>2637</v>
+        <v>2670</v>
       </c>
       <c r="H57" s="7">
-        <v>46133</v>
+        <v>46140</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
-        <v>9573777269</v>
+        <v>9441951134</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C58" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E58" s="2"/>
       <c r="G58" s="1">
-        <v>2636</v>
+        <v>2680</v>
       </c>
       <c r="H58" s="7">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
-        <v>9440936044</v>
+        <v>9100378294</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C59" s="1">
         <v>516</v>
       </c>
       <c r="E59" s="2"/>
       <c r="G59" s="1">
-        <v>2640</v>
+        <v>2678</v>
       </c>
       <c r="H59" s="7">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
-        <v>9394052517</v>
+        <v>9949781549</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C60" s="1">
-        <v>1116</v>
+        <v>501</v>
       </c>
       <c r="E60" s="2"/>
       <c r="G60" s="1">
-        <v>2639</v>
+        <v>2677</v>
       </c>
       <c r="H60" s="7">
-        <v>46134</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>224</v>
+        <v>46141</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
-        <v>9440581852</v>
+        <v>9849454393</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C61" s="1">
         <v>1116</v>
       </c>
       <c r="E61" s="2"/>
       <c r="G61" s="1">
-        <v>2641</v>
+        <v>2676</v>
       </c>
       <c r="H61" s="7">
-        <v>46135</v>
-      </c>
-      <c r="I61" s="9" t="s">
-        <v>272</v>
+        <v>46141</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
-        <v>9885500288</v>
+        <v>9704508381</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C62" s="1">
-        <v>6000</v>
+        <v>501</v>
       </c>
       <c r="E62" s="2"/>
       <c r="G62" s="1">
-        <v>2643</v>
+        <v>2700</v>
       </c>
       <c r="H62" s="7">
-        <v>46135</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>273</v>
+        <v>46142</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
-        <v>9440581852</v>
+        <v>9704508381</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C63" s="1">
-        <v>1116</v>
+        <v>501</v>
       </c>
       <c r="E63" s="2"/>
       <c r="G63" s="1">
-        <v>2642</v>
+        <v>2699</v>
       </c>
       <c r="H63" s="7">
-        <v>46135</v>
+        <v>46142</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
-        <v>9182177515</v>
+        <v>9849573741</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C64" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E64" s="2"/>
       <c r="G64" s="1">
-        <v>2647</v>
+        <v>2698</v>
       </c>
       <c r="H64" s="7">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
-        <v>9966086753</v>
+        <v>9866971604</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C65" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E65" s="2"/>
       <c r="G65" s="1">
-        <v>2646</v>
+        <v>2697</v>
       </c>
       <c r="H65" s="7">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
-        <v>9849453644</v>
+        <v>7989696010</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E66" s="2"/>
       <c r="G66" s="1">
-        <v>2645</v>
+        <v>2696</v>
       </c>
       <c r="H66" s="7">
-        <v>46136</v>
+        <v>46142</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
-        <v>9704353685</v>
+        <v>8978506070</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C67" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="1">
-        <v>2650</v>
+        <v>2695</v>
       </c>
       <c r="H67" s="7">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
-        <v>9000236644</v>
+        <v>7093848601</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C68" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E68" s="2"/>
       <c r="G68" s="1">
-        <v>2653</v>
+        <v>2693</v>
       </c>
       <c r="H68" s="7">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
-        <v>8019864314</v>
+        <v>9963350434</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C69" s="1">
-        <v>100</v>
+        <v>501</v>
       </c>
       <c r="E69" s="2"/>
       <c r="G69" s="1">
-        <v>2652</v>
+        <v>2692</v>
       </c>
       <c r="H69" s="7">
-        <v>46137</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>279</v>
+        <v>46142</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
-        <v>8919089789</v>
+        <v>9000166687</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C70" s="1">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E70" s="2"/>
       <c r="G70" s="1">
-        <v>2662</v>
+        <v>2691</v>
       </c>
       <c r="H70" s="7">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>280</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
-        <v>9441281179</v>
+        <v>9347648823</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71" s="1">
         <v>501</v>
       </c>
       <c r="E71" s="2"/>
       <c r="G71" s="1">
-        <v>2661</v>
+        <v>2690</v>
       </c>
       <c r="H71" s="7">
-        <v>46138</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>281</v>
-      </c>
+        <v>46142</v>
+      </c>
+      <c r="I71" s="2"/>
     </row>
     <row r="72" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
-        <v>9000249197</v>
+        <v>9394052517</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C72" s="1">
-        <v>501</v>
+        <v>2116</v>
       </c>
       <c r="E72" s="2"/>
       <c r="G72" s="1">
-        <v>2658</v>
+        <v>2689</v>
       </c>
       <c r="H72" s="7">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>282</v>
+        <v>201</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
-        <v>8187828483</v>
+        <v>8555910945</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C73" s="1">
-        <v>516</v>
+        <v>1002</v>
       </c>
       <c r="E73" s="2"/>
       <c r="G73" s="1">
-        <v>2657</v>
+        <v>2687</v>
       </c>
       <c r="H73" s="7">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
-        <v>9032031100</v>
+        <v>8897730033</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>77</v>
@@ -3400,17 +3277,19 @@
       </c>
       <c r="E74" s="2"/>
       <c r="G74" s="1">
-        <v>2656</v>
+        <v>2686</v>
       </c>
       <c r="H74" s="7">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="2"/>
+      <c r="A75" s="1">
+        <v>9542790682</v>
+      </c>
       <c r="B75" s="2" t="s">
         <v>78</v>
       </c>
@@ -3419,60 +3298,62 @@
       </c>
       <c r="E75" s="2"/>
       <c r="G75" s="1">
-        <v>2666</v>
+        <v>2685</v>
       </c>
       <c r="H75" s="7">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>285</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
-        <v>9966555091</v>
+        <v>9000586457</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C76" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E76" s="2"/>
       <c r="G76" s="1">
-        <v>2667</v>
+        <v>2682</v>
       </c>
       <c r="H76" s="7">
-        <v>46139</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>286</v>
+        <v>46142</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>9502176065</v>
+        <v>9849229230</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C77" s="1">
-        <v>501</v>
-      </c>
-      <c r="E77" s="2"/>
+        <v>1116</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>199</v>
+      </c>
       <c r="G77" s="1">
-        <v>2671</v>
+        <v>2681</v>
       </c>
       <c r="H77" s="7">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>9652202864</v>
+        <v>9963946248</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -3482,627 +3363,627 @@
       </c>
       <c r="E78" s="2"/>
       <c r="G78" s="1">
-        <v>2670</v>
+        <v>2703</v>
       </c>
       <c r="H78" s="7">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
-        <v>9441951134</v>
+        <v>9542790682</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C79" s="1">
-        <v>1116</v>
+        <v>2000</v>
       </c>
       <c r="E79" s="2"/>
       <c r="G79" s="1">
-        <v>2680</v>
+        <v>2706</v>
       </c>
       <c r="H79" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
-        <v>9100378294</v>
+        <v>9963350434</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C80" s="1">
         <v>516</v>
       </c>
       <c r="E80" s="2"/>
       <c r="G80" s="1">
-        <v>2678</v>
+        <v>2708</v>
       </c>
       <c r="H80" s="7">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
-        <v>9949781549</v>
+        <v>9440719985</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" s="1">
-        <v>501</v>
+        <v>5116</v>
       </c>
       <c r="E81" s="2"/>
       <c r="G81" s="1">
-        <v>2677</v>
+        <v>2709</v>
       </c>
       <c r="H81" s="7">
-        <v>46141</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>291</v>
+        <v>46142</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
-        <v>9849454393</v>
+        <v>9948908889</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C82" s="1">
         <v>1116</v>
       </c>
       <c r="E82" s="2"/>
       <c r="G82" s="1">
-        <v>2676</v>
+        <v>2688</v>
       </c>
       <c r="H82" s="7">
-        <v>46141</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>292</v>
+        <v>46142</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
-        <v>9704508381</v>
+        <v>9866971604</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C83" s="1">
         <v>501</v>
       </c>
       <c r="E83" s="2"/>
       <c r="G83" s="1">
-        <v>2700</v>
+        <v>2752</v>
       </c>
       <c r="H83" s="7">
         <v>46142</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
-        <v>9704508381</v>
+        <v>9177320518</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C84" s="1">
         <v>501</v>
       </c>
       <c r="E84" s="2"/>
       <c r="G84" s="1">
-        <v>2699</v>
+        <v>2753</v>
       </c>
       <c r="H84" s="7">
         <v>46142</v>
       </c>
-      <c r="I84" s="9" t="s">
-        <v>293</v>
+      <c r="I84" s="2" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
-        <v>9849573741</v>
+        <v>9866089651</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C85" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E85" s="2"/>
       <c r="G85" s="1">
-        <v>2698</v>
+        <v>2712</v>
       </c>
       <c r="H85" s="7">
         <v>46142</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
-        <v>9866971604</v>
+        <v>8247893200</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C86" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E86" s="2"/>
       <c r="G86" s="1">
-        <v>2697</v>
+        <v>2715</v>
       </c>
       <c r="H86" s="7">
         <v>46142</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
-        <v>7989696010</v>
+        <v>8464829471</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C87" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E87" s="2"/>
       <c r="G87" s="1">
-        <v>2696</v>
+        <v>1645</v>
       </c>
       <c r="H87" s="7">
         <v>46142</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>8978506070</v>
+        <v>8686874371</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C88" s="1">
-        <v>501</v>
+        <v>1116</v>
       </c>
       <c r="E88" s="2"/>
       <c r="G88" s="1">
-        <v>2695</v>
+        <v>1644</v>
       </c>
       <c r="H88" s="7">
         <v>46142</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>7093848601</v>
+        <v>9440048427</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C89" s="1">
-        <v>501</v>
+        <v>2116</v>
       </c>
       <c r="E89" s="2"/>
       <c r="G89" s="1">
-        <v>2693</v>
+        <v>2716</v>
       </c>
       <c r="H89" s="7">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>9963350434</v>
+        <v>9618546287</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C90" s="1">
-        <v>501</v>
+        <v>1116</v>
       </c>
       <c r="E90" s="2"/>
       <c r="G90" s="1">
-        <v>2692</v>
+        <v>2717</v>
       </c>
       <c r="H90" s="7">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>9000166687</v>
+        <v>7893101114</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="C91" s="1">
-        <v>501</v>
+        <v>1116</v>
       </c>
       <c r="E91" s="2"/>
       <c r="G91" s="1">
-        <v>2691</v>
+        <v>2718</v>
       </c>
       <c r="H91" s="7">
-        <v>46142</v>
+        <v>46144</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>234</v>
+        <v>277</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>9347648823</v>
+        <v>9849891431</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C92" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E92" s="2"/>
       <c r="G92" s="1">
-        <v>2690</v>
+        <v>2720</v>
       </c>
       <c r="H92" s="7">
-        <v>46142</v>
-      </c>
-      <c r="I92" s="2"/>
+        <v>46145</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="93" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>9394052517</v>
+        <v>9542127466</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C93" s="1">
-        <v>2116</v>
+        <v>516</v>
       </c>
       <c r="E93" s="2"/>
       <c r="G93" s="1">
-        <v>2689</v>
+        <v>2721</v>
       </c>
       <c r="H93" s="7">
-        <v>46142</v>
+        <v>46145</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>8555910945</v>
+        <v>7702309581</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C94" s="1">
-        <v>1002</v>
+        <v>516</v>
       </c>
       <c r="E94" s="2"/>
       <c r="G94" s="1">
-        <v>2687</v>
+        <v>2755</v>
       </c>
       <c r="H94" s="7">
-        <v>46142</v>
-      </c>
-      <c r="I94" s="9" t="s">
-        <v>300</v>
+        <v>46145</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
-        <v>8897730033</v>
+        <v>8919450845</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C95" s="1">
-        <v>501</v>
+        <v>1000</v>
       </c>
       <c r="E95" s="2"/>
       <c r="G95" s="1">
-        <v>2686</v>
+        <v>2726</v>
       </c>
       <c r="H95" s="7">
-        <v>46142</v>
+        <v>46147</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>9542790682</v>
+        <v>9390110502</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C96" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E96" s="2"/>
       <c r="G96" s="1">
-        <v>2685</v>
+        <v>2723</v>
       </c>
       <c r="H96" s="7">
-        <v>46142</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>264</v>
+        <v>46147</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
-        <v>9000586457</v>
+        <v>9642641483</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C97" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E97" s="2"/>
       <c r="G97" s="1">
-        <v>2682</v>
+        <v>2722</v>
       </c>
       <c r="H97" s="7">
-        <v>46142</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>262</v>
+        <v>46147</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="1">
-        <v>9849229230</v>
-      </c>
+      <c r="A98" s="2"/>
       <c r="B98" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C98" s="1">
-        <v>1116</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>220</v>
-      </c>
+        <v>3116</v>
+      </c>
+      <c r="E98" s="2"/>
       <c r="G98" s="1">
-        <v>2681</v>
+        <v>2727</v>
       </c>
       <c r="H98" s="7">
-        <v>46142</v>
+        <v>46147</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
-        <v>9963946248</v>
+        <v>8790720934</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="C99" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E99" s="2"/>
       <c r="G99" s="1">
-        <v>2703</v>
+        <v>2728</v>
       </c>
       <c r="H99" s="7">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
-        <v>9542790682</v>
+        <v>9701314079</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C100" s="1">
-        <v>2000</v>
-      </c>
-      <c r="E100" s="2"/>
+        <v>7000</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="G100" s="1">
-        <v>2706</v>
+        <v>2730</v>
       </c>
       <c r="H100" s="7">
-        <v>46142</v>
+        <v>46148</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
-        <v>9963350434</v>
+        <v>9676145376</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C101" s="1">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E101" s="2"/>
       <c r="G101" s="1">
-        <v>2708</v>
+        <v>2731</v>
       </c>
       <c r="H101" s="7">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>9440719985</v>
+        <v>7396790827</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" s="1">
-        <v>5116</v>
+        <v>216</v>
       </c>
       <c r="E102" s="2"/>
       <c r="G102" s="1">
-        <v>2709</v>
+        <v>2732</v>
       </c>
       <c r="H102" s="7">
-        <v>46142</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>306</v>
+        <v>46149</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>9948908889</v>
+        <v>9573661808</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C103" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E103" s="2"/>
       <c r="G103" s="1">
-        <v>2688</v>
+        <v>2736</v>
       </c>
       <c r="H103" s="7">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>9866971604</v>
+        <v>8919195596</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C104" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E104" s="2"/>
       <c r="G104" s="1">
-        <v>2752</v>
+        <v>2739</v>
       </c>
       <c r="H104" s="7">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>9177320518</v>
+        <v>8978869996</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C105" s="1">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="E105" s="2"/>
       <c r="G105" s="1">
-        <v>2753</v>
+        <v>2738</v>
       </c>
       <c r="H105" s="7">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>9866089651</v>
+        <v>9849250040</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C106" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E106" s="2"/>
       <c r="G106" s="1">
-        <v>2712</v>
+        <v>2742</v>
       </c>
       <c r="H106" s="7">
-        <v>46142</v>
+        <v>46151</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>8247893200</v>
+        <v>9848243113</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C107" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E107" s="2"/>
       <c r="G107" s="1">
-        <v>2715</v>
+        <v>2740</v>
       </c>
       <c r="H107" s="7">
-        <v>46142</v>
+        <v>46151</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>8464829471</v>
+        <v>8247533197</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>108</v>
@@ -4112,123 +3993,123 @@
       </c>
       <c r="E108" s="2"/>
       <c r="G108" s="1">
-        <v>1645</v>
+        <v>2749</v>
       </c>
       <c r="H108" s="7">
-        <v>46142</v>
-      </c>
-      <c r="I108" s="9" t="s">
-        <v>312</v>
+        <v>46152</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>8686874371</v>
+        <v>7893955946</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C109" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E109" s="2"/>
       <c r="G109" s="1">
-        <v>1644</v>
+        <v>2745</v>
       </c>
       <c r="H109" s="7">
-        <v>46142</v>
+        <v>46152</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>9440048427</v>
+        <v>7382852014</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C110" s="1">
-        <v>2116</v>
+        <v>900</v>
       </c>
       <c r="E110" s="2"/>
       <c r="G110" s="1">
-        <v>2716</v>
+        <v>2747</v>
       </c>
       <c r="H110" s="7">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>9618546287</v>
+        <v>9182954986</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C111" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E111" s="2"/>
       <c r="G111" s="1">
-        <v>2717</v>
+        <v>2746</v>
       </c>
       <c r="H111" s="7">
-        <v>46144</v>
-      </c>
-      <c r="I111" s="9" t="s">
-        <v>315</v>
+        <v>46152</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
-        <v>7893101114</v>
+        <v>9700121401</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C112" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E112" s="2"/>
       <c r="G112" s="1">
-        <v>2718</v>
+        <v>2763</v>
       </c>
       <c r="H112" s="7">
-        <v>46144</v>
+        <v>46153</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>9849891431</v>
+        <v>9014955065</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C113" s="1">
-        <v>516</v>
+        <v>1500</v>
       </c>
       <c r="E113" s="2"/>
       <c r="G113" s="1">
-        <v>2720</v>
+        <v>2769</v>
       </c>
       <c r="H113" s="7">
-        <v>46145</v>
+        <v>46154</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>9542127466</v>
+        <v>8328132147</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>114</v>
@@ -4238,60 +4119,60 @@
       </c>
       <c r="E114" s="2"/>
       <c r="G114" s="1">
-        <v>2721</v>
+        <v>2768</v>
       </c>
       <c r="H114" s="7">
-        <v>46145</v>
+        <v>46154</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>7702309581</v>
+        <v>8374842308</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C115" s="1">
-        <v>516</v>
+        <v>5001</v>
       </c>
       <c r="E115" s="2"/>
       <c r="G115" s="1">
-        <v>2755</v>
+        <v>2770</v>
       </c>
       <c r="H115" s="7">
-        <v>46145</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>319</v>
+        <v>46154</v>
+      </c>
+      <c r="I115" s="9" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>8919450845</v>
+        <v>9700011128</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C116" s="1">
-        <v>1000</v>
+        <v>516</v>
       </c>
       <c r="E116" s="2"/>
       <c r="G116" s="1">
-        <v>2726</v>
+        <v>2771</v>
       </c>
       <c r="H116" s="7">
-        <v>46147</v>
-      </c>
-      <c r="I116" s="9" t="s">
-        <v>320</v>
+        <v>46154</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>9390110502</v>
+        <v>9963555379</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>117</v>
@@ -4301,165 +4182,165 @@
       </c>
       <c r="E117" s="2"/>
       <c r="G117" s="1">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="H117" s="7">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="I117" s="9" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>9642641483</v>
+        <v>6303260548</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C118" s="1">
-        <v>1116</v>
+        <v>500</v>
       </c>
       <c r="E118" s="2"/>
       <c r="G118" s="1">
-        <v>2722</v>
+        <v>2778</v>
       </c>
       <c r="H118" s="7">
-        <v>46147</v>
-      </c>
-      <c r="I118" s="9" t="s">
-        <v>322</v>
+        <v>46157</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="2"/>
+      <c r="A119" s="1">
+        <v>9866848688</v>
+      </c>
       <c r="B119" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C119" s="1">
-        <v>3116</v>
+        <v>516</v>
       </c>
       <c r="E119" s="2"/>
       <c r="G119" s="1">
-        <v>2727</v>
+        <v>2779</v>
       </c>
       <c r="H119" s="7">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="1">
-        <v>8790720934</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C120" s="1">
-        <v>516</v>
+      <c r="A120" s="3">
+        <v>7013220720</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C120" s="3">
+        <v>316</v>
       </c>
       <c r="E120" s="2"/>
-      <c r="G120" s="1">
-        <v>2728</v>
-      </c>
-      <c r="H120" s="7">
-        <v>46148</v>
-      </c>
-      <c r="I120" s="9" t="s">
-        <v>324</v>
+      <c r="G120" s="3">
+        <v>2777</v>
+      </c>
+      <c r="H120" s="8">
+        <v>46157</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>9701314079</v>
+        <v>9000166687</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="C121" s="1">
-        <v>7000</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>221</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="E121" s="2"/>
       <c r="G121" s="1">
-        <v>2730</v>
+        <v>2785</v>
       </c>
       <c r="H121" s="7">
-        <v>46148</v>
+        <v>46158</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>9676145376</v>
+        <v>9491533233</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C122" s="1">
-        <v>520</v>
+        <v>1500</v>
       </c>
       <c r="E122" s="2"/>
       <c r="G122" s="1">
-        <v>2731</v>
+        <v>2784</v>
       </c>
       <c r="H122" s="7">
-        <v>46149</v>
+        <v>46158</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>7396790827</v>
+        <v>9866574381</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C123" s="1">
-        <v>216</v>
+        <v>516</v>
       </c>
       <c r="E123" s="2"/>
       <c r="G123" s="1">
-        <v>2732</v>
+        <v>2781</v>
       </c>
       <c r="H123" s="7">
-        <v>46149</v>
+        <v>46158</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>9573661808</v>
+        <v>9848072869</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C124" s="1">
-        <v>516</v>
+        <v>2511</v>
       </c>
       <c r="E124" s="2"/>
       <c r="G124" s="1">
-        <v>2736</v>
+        <v>2780</v>
       </c>
       <c r="H124" s="7">
-        <v>46150</v>
-      </c>
-      <c r="I124" s="9" t="s">
-        <v>328</v>
+        <v>46158</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>8919195596</v>
+        <v>8978662256</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>124</v>
@@ -4469,81 +4350,81 @@
       </c>
       <c r="E125" s="2"/>
       <c r="G125" s="1">
-        <v>2739</v>
+        <v>2788</v>
       </c>
       <c r="H125" s="7">
-        <v>46150</v>
+        <v>46159</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>8978869996</v>
+        <v>9032883423</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C126" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E126" s="2"/>
       <c r="G126" s="1">
-        <v>2738</v>
+        <v>2787</v>
       </c>
       <c r="H126" s="7">
-        <v>46150</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>330</v>
+        <v>46159</v>
+      </c>
+      <c r="I126" s="9" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>9849250040</v>
+        <v>9550055953</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C127" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E127" s="2"/>
       <c r="G127" s="1">
-        <v>2742</v>
+        <v>2786</v>
       </c>
       <c r="H127" s="7">
-        <v>46151</v>
+        <v>46159</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>9848243113</v>
+        <v>9505861241</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C128" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E128" s="2"/>
       <c r="G128" s="1">
-        <v>2740</v>
+        <v>2792</v>
       </c>
       <c r="H128" s="7">
-        <v>46151</v>
+        <v>46162</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>8247533197</v>
+        <v>7032560551</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>128</v>
@@ -4553,60 +4434,60 @@
       </c>
       <c r="E129" s="2"/>
       <c r="G129" s="1">
-        <v>2749</v>
+        <v>2797</v>
       </c>
       <c r="H129" s="7">
-        <v>46152</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>333</v>
+        <v>46165</v>
+      </c>
+      <c r="I129" s="9" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>7893955946</v>
+        <v>8790993697</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C130" s="1">
-        <v>516</v>
+        <v>3116</v>
       </c>
       <c r="E130" s="2"/>
       <c r="G130" s="1">
-        <v>2745</v>
+        <v>2796</v>
       </c>
       <c r="H130" s="7">
-        <v>46152</v>
+        <v>46165</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>7382852014</v>
+        <v>9949107990</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C131" s="1">
-        <v>900</v>
+        <v>1116</v>
       </c>
       <c r="E131" s="2"/>
       <c r="G131" s="1">
-        <v>2747</v>
+        <v>2801</v>
       </c>
       <c r="H131" s="7">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>9182954986</v>
+        <v>8686218899</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>131</v>
@@ -4616,250 +4497,248 @@
       </c>
       <c r="E132" s="2"/>
       <c r="G132" s="1">
-        <v>2746</v>
+        <v>2798</v>
       </c>
       <c r="H132" s="7">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>9700121401</v>
+        <v>9177011622</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C133" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E133" s="2"/>
       <c r="G133" s="1">
-        <v>2763</v>
+        <v>2799</v>
       </c>
       <c r="H133" s="7">
-        <v>46153</v>
+        <v>46166</v>
       </c>
       <c r="I133" s="9" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>9014955065</v>
+        <v>9514398842</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C134" s="1">
-        <v>1500</v>
+        <v>516</v>
       </c>
       <c r="E134" s="2"/>
       <c r="G134" s="1">
-        <v>2769</v>
+        <v>2805</v>
       </c>
       <c r="H134" s="7">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="I134" s="9" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>8328132147</v>
+        <v>9989021735</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C135" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E135" s="2"/>
       <c r="G135" s="1">
-        <v>2768</v>
+        <v>2804</v>
       </c>
       <c r="H135" s="7">
-        <v>46154</v>
-      </c>
-      <c r="I135" s="9" t="s">
-        <v>339</v>
+        <v>46167</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
-        <v>8374842308</v>
+        <v>9701314079</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C136" s="1">
-        <v>5001</v>
+        <v>5116</v>
       </c>
       <c r="E136" s="2"/>
       <c r="G136" s="1">
-        <v>2770</v>
+        <v>2806</v>
       </c>
       <c r="H136" s="7">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="I136" s="9" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>9700011128</v>
+        <v>9440086356</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C137" s="1">
-        <v>516</v>
+        <v>1001</v>
       </c>
       <c r="E137" s="2"/>
       <c r="G137" s="1">
-        <v>2771</v>
+        <v>2815</v>
       </c>
       <c r="H137" s="7">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>9963555379</v>
+        <v>9963841470</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C138" s="1">
         <v>516</v>
       </c>
       <c r="E138" s="2"/>
       <c r="G138" s="1">
-        <v>2773</v>
+        <v>2813</v>
       </c>
       <c r="H138" s="7">
-        <v>46155</v>
-      </c>
-      <c r="I138" s="9" t="s">
-        <v>342</v>
+        <v>46169</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
-        <v>6303260548</v>
+        <v>9177320518</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C139" s="1">
-        <v>500</v>
+        <v>1116</v>
       </c>
       <c r="E139" s="2"/>
       <c r="G139" s="1">
-        <v>2778</v>
+        <v>2812</v>
       </c>
       <c r="H139" s="7">
-        <v>46157</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>343</v>
+        <v>46169</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
-        <v>9866848688</v>
+        <v>9550453915</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C140" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E140" s="2"/>
       <c r="G140" s="1">
-        <v>2779</v>
+        <v>2811</v>
       </c>
       <c r="H140" s="7">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="I140" s="9" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="3">
-        <v>7013220720</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C141" s="3">
-        <v>316</v>
+      <c r="A141" s="1">
+        <v>8008644204</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C141" s="1">
+        <v>516</v>
       </c>
       <c r="E141" s="2"/>
-      <c r="G141" s="3">
-        <v>2777</v>
-      </c>
-      <c r="H141" s="8">
-        <v>46157</v>
-      </c>
-      <c r="I141" s="5" t="s">
-        <v>345</v>
+      <c r="G141" s="1">
+        <v>2810</v>
+      </c>
+      <c r="H141" s="7">
+        <v>46169</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
-        <v>9000166687</v>
+        <v>9700925859</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="C142" s="1">
-        <v>10000</v>
+        <v>516</v>
       </c>
       <c r="E142" s="2"/>
       <c r="G142" s="1">
-        <v>2785</v>
+        <v>2808</v>
       </c>
       <c r="H142" s="7">
-        <v>46158</v>
-      </c>
-      <c r="I142" s="9" t="s">
-        <v>346</v>
+        <v>46169</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
-        <v>9491533233</v>
+        <v>8008260508</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C143" s="1">
-        <v>1500</v>
+        <v>632</v>
       </c>
       <c r="E143" s="2"/>
       <c r="G143" s="1">
-        <v>2784</v>
+        <v>2807</v>
       </c>
       <c r="H143" s="7">
-        <v>46158</v>
+        <v>46169</v>
       </c>
       <c r="I143" s="9" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="1">
-        <v>9866574381</v>
-      </c>
+      <c r="A144" s="2"/>
       <c r="B144" s="2" t="s">
         <v>142</v>
       </c>
@@ -4868,40 +4747,38 @@
       </c>
       <c r="E144" s="2"/>
       <c r="G144" s="1">
-        <v>2781</v>
+        <v>2820</v>
       </c>
       <c r="H144" s="7">
-        <v>46158</v>
+        <v>46170</v>
       </c>
       <c r="I144" s="9" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
-        <v>9848072869</v>
+        <v>8179479750</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C145" s="1">
-        <v>2511</v>
+        <v>516</v>
       </c>
       <c r="E145" s="2"/>
       <c r="G145" s="1">
-        <v>2780</v>
+        <v>2816</v>
       </c>
       <c r="H145" s="7">
-        <v>46158</v>
-      </c>
-      <c r="I145" s="2" t="s">
-        <v>349</v>
+        <v>46170</v>
+      </c>
+      <c r="I145" s="9" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="1">
-        <v>8978662256</v>
-      </c>
+      <c r="A146" s="2"/>
       <c r="B146" s="2" t="s">
         <v>144</v>
       </c>
@@ -4910,60 +4787,60 @@
       </c>
       <c r="E146" s="2"/>
       <c r="G146" s="1">
-        <v>2788</v>
+        <v>2819</v>
       </c>
       <c r="H146" s="7">
-        <v>46159</v>
-      </c>
-      <c r="I146" s="9" t="s">
-        <v>350</v>
+        <v>46170</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
-        <v>9032883423</v>
+        <v>7680972931</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C147" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E147" s="2"/>
       <c r="G147" s="1">
-        <v>2787</v>
+        <v>2822</v>
       </c>
       <c r="H147" s="7">
-        <v>46159</v>
+        <v>46171</v>
       </c>
       <c r="I147" s="9" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
-        <v>9550055953</v>
+        <v>9490959613</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C148" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E148" s="2"/>
       <c r="G148" s="1">
-        <v>2786</v>
+        <v>2823</v>
       </c>
       <c r="H148" s="7">
-        <v>46159</v>
+        <v>46172</v>
       </c>
       <c r="I148" s="9" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
-        <v>9505861241</v>
+        <v>8123323094</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>147</v>
@@ -4973,1707 +4850,1459 @@
       </c>
       <c r="E149" s="2"/>
       <c r="G149" s="1">
-        <v>2792</v>
+        <v>2824</v>
       </c>
       <c r="H149" s="7">
-        <v>46162</v>
-      </c>
-      <c r="I149" s="9" t="s">
-        <v>353</v>
+        <v>46172</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>7032560551</v>
+        <v>9848898975</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="C150" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E150" s="2"/>
       <c r="G150" s="1">
-        <v>2797</v>
+        <v>2828</v>
       </c>
       <c r="H150" s="7">
-        <v>46165</v>
+        <v>46173</v>
       </c>
       <c r="I150" s="9" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
-        <v>8790993697</v>
+        <v>9866764458</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C151" s="1">
-        <v>3116</v>
+        <v>516</v>
       </c>
       <c r="E151" s="2"/>
       <c r="G151" s="1">
-        <v>2796</v>
+        <v>2827</v>
       </c>
       <c r="H151" s="7">
-        <v>46165</v>
+        <v>46173</v>
       </c>
       <c r="I151" s="9" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>9949107990</v>
+        <v>6302419390</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C152" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E152" s="2"/>
       <c r="G152" s="1">
-        <v>2801</v>
+        <v>2826</v>
       </c>
       <c r="H152" s="7">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="I152" s="9" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>8686218899</v>
+        <v>9502450401</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C153" s="1">
         <v>516</v>
       </c>
       <c r="E153" s="2"/>
       <c r="G153" s="1">
-        <v>2798</v>
+        <v>2825</v>
       </c>
       <c r="H153" s="7">
-        <v>46166</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>357</v>
+        <v>46173</v>
+      </c>
+      <c r="I153" s="9" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>9177011622</v>
+        <v>8790752657</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C154" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E154" s="2"/>
       <c r="G154" s="1">
-        <v>2799</v>
+        <v>2830</v>
       </c>
       <c r="H154" s="7">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="I154" s="9" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
-        <v>9514398842</v>
+        <v>7981896097</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="C155" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E155" s="2"/>
       <c r="G155" s="1">
-        <v>2805</v>
+        <v>2834</v>
       </c>
       <c r="H155" s="7">
-        <v>46167</v>
+        <v>46176</v>
       </c>
       <c r="I155" s="9" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>9989021735</v>
+        <v>9000166687</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="C156" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E156" s="2"/>
       <c r="G156" s="1">
-        <v>2804</v>
+        <v>2836</v>
       </c>
       <c r="H156" s="7">
-        <v>46167</v>
+        <v>46176</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>360</v>
+        <v>307</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>9701314079</v>
+        <v>9908398337</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="C157" s="1">
-        <v>5116</v>
+        <v>516</v>
       </c>
       <c r="E157" s="2"/>
       <c r="G157" s="1">
-        <v>2806</v>
+        <v>2839</v>
       </c>
       <c r="H157" s="7">
-        <v>46168</v>
+        <v>46178</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>9440086356</v>
+        <v>9573168406</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C158" s="1">
-        <v>1001</v>
+        <v>1032</v>
       </c>
       <c r="E158" s="2"/>
       <c r="G158" s="1">
-        <v>2815</v>
+        <v>2842</v>
       </c>
       <c r="H158" s="7">
-        <v>46169</v>
-      </c>
-      <c r="I158" s="2" t="s">
-        <v>362</v>
+        <v>46178</v>
+      </c>
+      <c r="I158" s="9" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>9963841470</v>
+        <v>99129137992</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C159" s="1">
         <v>516</v>
       </c>
       <c r="E159" s="2"/>
       <c r="G159" s="1">
-        <v>2813</v>
+        <v>2846</v>
       </c>
       <c r="H159" s="7">
-        <v>46169</v>
+        <v>46180</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>9177320518</v>
+        <v>9642836595</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C160" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E160" s="2"/>
       <c r="G160" s="1">
-        <v>2812</v>
+        <v>2849</v>
       </c>
       <c r="H160" s="7">
-        <v>46169</v>
-      </c>
-      <c r="I160" s="9" t="s">
-        <v>364</v>
+        <v>46180</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
-        <v>9550453915</v>
+        <v>9949511666</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C161" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E161" s="2"/>
       <c r="G161" s="1">
-        <v>2811</v>
+        <v>2848</v>
       </c>
       <c r="H161" s="7">
-        <v>46169</v>
+        <v>46180</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>8008644204</v>
+        <v>7382855453</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C162" s="1">
-        <v>516</v>
+        <v>3116</v>
       </c>
       <c r="E162" s="2"/>
       <c r="G162" s="1">
-        <v>2810</v>
+        <v>2843</v>
       </c>
       <c r="H162" s="7">
-        <v>46169</v>
+        <v>46180</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>9700925859</v>
+        <v>9640668787</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C163" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E163" s="2"/>
       <c r="G163" s="1">
-        <v>2808</v>
+        <v>2850</v>
       </c>
       <c r="H163" s="7">
-        <v>46169</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>366</v>
+        <v>46180</v>
+      </c>
+      <c r="I163" s="9" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>8008260508</v>
+        <v>9866568921</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C164" s="1">
-        <v>632</v>
+        <v>1516</v>
       </c>
       <c r="E164" s="2"/>
       <c r="G164" s="1">
-        <v>2807</v>
+        <v>2880</v>
       </c>
       <c r="H164" s="7">
-        <v>46169</v>
-      </c>
-      <c r="I164" s="9" t="s">
-        <v>367</v>
+        <v>46180</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="2"/>
+      <c r="A165" s="1">
+        <v>9948525954</v>
+      </c>
       <c r="B165" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C165" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E165" s="2"/>
       <c r="G165" s="1">
-        <v>2820</v>
+        <v>2852</v>
       </c>
       <c r="H165" s="7">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="I165" s="9" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>8179479750</v>
+        <v>9849447444</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C166" s="1">
         <v>516</v>
       </c>
       <c r="E166" s="2"/>
       <c r="G166" s="1">
-        <v>2816</v>
+        <v>2855</v>
       </c>
       <c r="H166" s="7">
-        <v>46170</v>
-      </c>
-      <c r="I166" s="9" t="s">
-        <v>369</v>
+        <v>46182</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="2"/>
+      <c r="A167" s="1">
+        <v>9440724289</v>
+      </c>
       <c r="B167" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C167" s="1">
         <v>516</v>
       </c>
       <c r="E167" s="2"/>
       <c r="G167" s="1">
-        <v>2819</v>
+        <v>2853</v>
       </c>
       <c r="H167" s="7">
-        <v>46170</v>
-      </c>
-      <c r="I167" s="2" t="s">
-        <v>370</v>
+        <v>46182</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>7680972931</v>
+        <v>9848789122</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C168" s="1">
-        <v>516</v>
+        <v>6000</v>
       </c>
       <c r="E168" s="2"/>
       <c r="G168" s="1">
-        <v>2822</v>
+        <v>2854</v>
       </c>
       <c r="H168" s="7">
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="I168" s="9" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
-        <v>9490959613</v>
+        <v>9642641483</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C169" s="1">
-        <v>1116</v>
+        <v>1200</v>
       </c>
       <c r="E169" s="2"/>
       <c r="G169" s="1">
-        <v>2823</v>
+        <v>2859</v>
       </c>
       <c r="H169" s="7">
-        <v>46172</v>
-      </c>
-      <c r="I169" s="9" t="s">
-        <v>372</v>
+        <v>46184</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>8123323094</v>
+        <v>7845806724</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C170" s="1">
-        <v>516</v>
+        <v>3116</v>
       </c>
       <c r="E170" s="2"/>
       <c r="G170" s="1">
-        <v>2824</v>
+        <v>2858</v>
       </c>
       <c r="H170" s="7">
-        <v>46172</v>
-      </c>
-      <c r="I170" s="2" t="s">
-        <v>373</v>
+        <v>46184</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>9848898975</v>
+        <v>8309382130</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>57</v>
+        <v>166</v>
       </c>
       <c r="C171" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E171" s="2"/>
       <c r="G171" s="1">
-        <v>2828</v>
+        <v>2866</v>
       </c>
       <c r="H171" s="7">
-        <v>46173</v>
+        <v>46184</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
-        <v>9866764458</v>
+        <v>9963841470</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C172" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E172" s="2"/>
       <c r="G172" s="1">
-        <v>2827</v>
+        <v>2865</v>
       </c>
       <c r="H172" s="7">
-        <v>46173</v>
+        <v>46184</v>
       </c>
       <c r="I172" s="9" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
-        <v>6302419390</v>
+        <v>9533271880</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C173" s="1">
         <v>516</v>
       </c>
       <c r="E173" s="2"/>
       <c r="G173" s="1">
-        <v>2826</v>
+        <v>2864</v>
       </c>
       <c r="H173" s="7">
-        <v>46173</v>
+        <v>46184</v>
       </c>
       <c r="I173" s="9" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
-        <v>9502450401</v>
+        <v>9949438325</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C174" s="1">
         <v>516</v>
       </c>
       <c r="E174" s="2"/>
       <c r="G174" s="1">
-        <v>2825</v>
+        <v>2863</v>
       </c>
       <c r="H174" s="7">
-        <v>46173</v>
+        <v>46184</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
-        <v>8790752657</v>
+        <v>9440599332</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C175" s="1">
         <v>516</v>
       </c>
       <c r="E175" s="2"/>
       <c r="G175" s="1">
-        <v>2830</v>
+        <v>2871</v>
       </c>
       <c r="H175" s="7">
-        <v>46173</v>
+        <v>46185</v>
       </c>
       <c r="I175" s="9" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
-        <v>7981896097</v>
+        <v>9533488612</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="C176" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E176" s="2"/>
       <c r="G176" s="1">
-        <v>2834</v>
+        <v>2869</v>
       </c>
       <c r="H176" s="7">
-        <v>46176</v>
-      </c>
-      <c r="I176" s="9" t="s">
-        <v>379</v>
+        <v>46185</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
-        <v>9000166687</v>
+        <v>7382326342</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="C177" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E177" s="2"/>
       <c r="G177" s="1">
-        <v>2836</v>
+        <v>2868</v>
       </c>
       <c r="H177" s="7">
-        <v>46176</v>
-      </c>
-      <c r="I177" s="2" t="s">
-        <v>346</v>
+        <v>46185</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
-        <v>9908398337</v>
+        <v>7036354527</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C178" s="1">
         <v>516</v>
       </c>
       <c r="E178" s="2"/>
       <c r="G178" s="1">
-        <v>2839</v>
+        <v>2872</v>
       </c>
       <c r="H178" s="7">
-        <v>46178</v>
+        <v>46186</v>
       </c>
       <c r="I178" s="9" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
-        <v>9573168406</v>
+        <v>9030493457</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C179" s="1">
-        <v>1032</v>
+        <v>516</v>
       </c>
       <c r="E179" s="2"/>
       <c r="G179" s="1">
-        <v>2842</v>
+        <v>2874</v>
       </c>
       <c r="H179" s="7">
-        <v>46178</v>
+        <v>46186</v>
       </c>
       <c r="I179" s="9" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
-        <v>99129137992</v>
+        <v>6304136095</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C180" s="1">
-        <v>516</v>
+        <v>1116</v>
       </c>
       <c r="E180" s="2"/>
       <c r="G180" s="1">
-        <v>2846</v>
+        <v>2876</v>
       </c>
       <c r="H180" s="7">
-        <v>46180</v>
-      </c>
-      <c r="I180" s="2" t="s">
-        <v>382</v>
+        <v>46186</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
-        <v>9642836595</v>
+        <v>9030924337</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C181" s="1">
         <v>516</v>
       </c>
       <c r="E181" s="2"/>
       <c r="G181" s="1">
-        <v>2849</v>
+        <v>2875</v>
       </c>
       <c r="H181" s="7">
-        <v>46180</v>
+        <v>46186</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="1">
-        <v>9949511666</v>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="C182" s="1">
         <v>516</v>
       </c>
       <c r="E182" s="2"/>
       <c r="G182" s="1">
-        <v>2848</v>
+        <v>2887</v>
       </c>
       <c r="H182" s="7">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="I182" s="9" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
-        <v>7382855453</v>
+        <v>9347310459</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C183" s="1">
-        <v>3116</v>
+        <v>1116</v>
       </c>
       <c r="E183" s="2"/>
       <c r="G183" s="1">
-        <v>2843</v>
+        <v>2884</v>
       </c>
       <c r="H183" s="7">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="I183" s="9" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
-        <v>9640668787</v>
+        <v>9032163034</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C184" s="1">
-        <v>1116</v>
+        <v>1016</v>
       </c>
       <c r="E184" s="2"/>
       <c r="G184" s="1">
-        <v>2850</v>
+        <v>2883</v>
       </c>
       <c r="H184" s="7">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="I184" s="9" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
-        <v>9866568921</v>
+        <v>8142938181</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>179</v>
       </c>
       <c r="C185" s="1">
-        <v>1516</v>
+        <v>516</v>
       </c>
       <c r="E185" s="2"/>
       <c r="G185" s="1">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="H185" s="7">
-        <v>46180</v>
-      </c>
-      <c r="I185" s="2" t="s">
-        <v>387</v>
+        <v>46187</v>
+      </c>
+      <c r="I185" s="9" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
-        <v>9948525954</v>
+        <v>9000249197</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="C186" s="1">
         <v>1116</v>
       </c>
       <c r="E186" s="2"/>
       <c r="G186" s="1">
-        <v>2852</v>
+        <v>2879</v>
       </c>
       <c r="H186" s="7">
-        <v>46181</v>
+        <v>46187</v>
       </c>
       <c r="I186" s="9" t="s">
-        <v>388</v>
+        <v>335</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
-        <v>9849447444</v>
+        <v>7396120056</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C187" s="1">
-        <v>516</v>
+        <v>5000</v>
       </c>
       <c r="E187" s="2"/>
       <c r="G187" s="1">
-        <v>2855</v>
+        <v>2878</v>
       </c>
       <c r="H187" s="7">
-        <v>46182</v>
+        <v>46187</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
-        <v>9440724289</v>
+        <v>9618682686</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C188" s="1">
         <v>516</v>
       </c>
       <c r="E188" s="2"/>
       <c r="G188" s="1">
-        <v>2853</v>
+        <v>2889</v>
       </c>
       <c r="H188" s="7">
-        <v>46182</v>
-      </c>
-      <c r="I188" s="9" t="s">
-        <v>390</v>
-      </c>
+        <v>46187</v>
+      </c>
+      <c r="I188" s="2"/>
     </row>
     <row r="189" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
-        <v>9848789122</v>
+        <v>9618961007</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C189" s="1">
-        <v>6000</v>
+        <v>516</v>
       </c>
       <c r="E189" s="2"/>
       <c r="G189" s="1">
-        <v>2854</v>
+        <v>2892</v>
       </c>
       <c r="H189" s="7">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="I189" s="9" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
-        <v>9642641483</v>
+        <v>9951719178</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C190" s="1">
-        <v>1200</v>
+        <v>516</v>
       </c>
       <c r="E190" s="2"/>
       <c r="G190" s="1">
-        <v>2859</v>
+        <v>2891</v>
       </c>
       <c r="H190" s="7">
-        <v>46184</v>
-      </c>
-      <c r="I190" s="2" t="s">
-        <v>392</v>
+        <v>46188</v>
+      </c>
+      <c r="I190" s="9" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
-        <v>7845806724</v>
+        <v>7661854477</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C191" s="1">
-        <v>3116</v>
+        <v>516</v>
       </c>
       <c r="E191" s="2"/>
       <c r="G191" s="1">
-        <v>2858</v>
+        <v>2890</v>
       </c>
       <c r="H191" s="7">
-        <v>46184</v>
-      </c>
-      <c r="I191" s="9" t="s">
-        <v>393</v>
+        <v>46188</v>
+      </c>
+      <c r="I191" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
-        <v>8309382130</v>
+        <v>7396120056</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C192" s="1">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="E192" s="2"/>
       <c r="G192" s="1">
-        <v>2866</v>
+        <v>2899</v>
       </c>
       <c r="H192" s="7">
-        <v>46184</v>
-      </c>
-      <c r="I192" s="9" t="s">
-        <v>394</v>
-      </c>
+        <v>46189</v>
+      </c>
+      <c r="I192" s="2"/>
     </row>
     <row r="193" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
-        <v>9963841470</v>
+        <v>9989615167</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C193" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E193" s="2"/>
       <c r="G193" s="1">
-        <v>2865</v>
+        <v>2896</v>
       </c>
       <c r="H193" s="7">
-        <v>46184</v>
-      </c>
-      <c r="I193" s="9" t="s">
-        <v>395</v>
+        <v>46190</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
-        <v>9533271880</v>
+        <v>9700685055</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C194" s="1">
         <v>516</v>
       </c>
       <c r="E194" s="2"/>
       <c r="G194" s="1">
-        <v>2864</v>
+        <v>2355</v>
       </c>
       <c r="H194" s="7">
-        <v>46184</v>
+        <v>46193</v>
       </c>
       <c r="I194" s="9" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
-        <v>9949438325</v>
+        <v>9493936707</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C195" s="1">
-        <v>516</v>
+        <v>1632</v>
       </c>
       <c r="E195" s="2"/>
       <c r="G195" s="1">
-        <v>2863</v>
+        <v>2354</v>
       </c>
       <c r="H195" s="7">
-        <v>46184</v>
+        <v>46193</v>
       </c>
       <c r="I195" s="9" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
-        <v>9440599332</v>
+        <v>9866392184</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C196" s="1">
         <v>516</v>
       </c>
       <c r="E196" s="2"/>
       <c r="G196" s="1">
-        <v>2871</v>
+        <v>2353</v>
       </c>
       <c r="H196" s="7">
-        <v>46185</v>
+        <v>46193</v>
       </c>
       <c r="I196" s="9" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
-        <v>9533488612</v>
+        <v>7893998695</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C197" s="1">
         <v>516</v>
       </c>
       <c r="E197" s="2"/>
       <c r="G197" s="1">
-        <v>2869</v>
+        <v>2359</v>
       </c>
       <c r="H197" s="7">
-        <v>46185</v>
-      </c>
-      <c r="I197" s="2" t="s">
-        <v>399</v>
+        <v>46194</v>
+      </c>
+      <c r="I197" s="9" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
-        <v>7382326342</v>
+        <v>7893998695</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C198" s="1">
         <v>1116</v>
       </c>
       <c r="E198" s="2"/>
       <c r="G198" s="1">
-        <v>2868</v>
+        <v>2358</v>
       </c>
       <c r="H198" s="7">
-        <v>46185</v>
+        <v>46194</v>
       </c>
       <c r="I198" s="9" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
-        <v>7036354527</v>
+        <v>9652489430</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C199" s="1">
         <v>516</v>
       </c>
       <c r="E199" s="2"/>
       <c r="G199" s="1">
-        <v>2872</v>
+        <v>2357</v>
       </c>
       <c r="H199" s="7">
-        <v>46186</v>
+        <v>46194</v>
       </c>
       <c r="I199" s="9" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
-        <v>9030493457</v>
+        <v>7780487639</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C200" s="1">
         <v>516</v>
       </c>
       <c r="E200" s="2"/>
       <c r="G200" s="1">
-        <v>2874</v>
+        <v>2361</v>
       </c>
       <c r="H200" s="7">
-        <v>46186</v>
+        <v>46195</v>
       </c>
       <c r="I200" s="9" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
-        <v>6304136095</v>
+        <v>9949034545</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C201" s="1">
         <v>1116</v>
       </c>
       <c r="E201" s="2"/>
       <c r="G201" s="1">
-        <v>2876</v>
+        <v>2360</v>
       </c>
       <c r="H201" s="7">
-        <v>46186</v>
+        <v>46195</v>
       </c>
       <c r="I201" s="9" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
-        <v>9030924337</v>
+        <v>8341587969</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C202" s="1">
-        <v>516</v>
+        <v>1016</v>
       </c>
       <c r="E202" s="2"/>
       <c r="G202" s="1">
-        <v>2875</v>
+        <v>2364</v>
       </c>
       <c r="H202" s="7">
-        <v>46186</v>
-      </c>
-      <c r="I202" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>138</v>
+        <v>46196</v>
+      </c>
+      <c r="I202" s="10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="4">
+        <v>6281659358</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="C203" s="1">
         <v>516</v>
       </c>
       <c r="E203" s="2"/>
       <c r="G203" s="1">
-        <v>2887</v>
+        <v>2365</v>
       </c>
       <c r="H203" s="7">
-        <v>46187</v>
-      </c>
-      <c r="I203" s="9" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46197</v>
+      </c>
+      <c r="I203" s="11" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
-        <v>9347310459</v>
+        <v>9440086356</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C204" s="1">
-        <v>1116</v>
+        <v>501</v>
       </c>
       <c r="E204" s="2"/>
       <c r="G204" s="1">
-        <v>2884</v>
+        <v>2369</v>
       </c>
       <c r="H204" s="7">
-        <v>46187</v>
-      </c>
-      <c r="I204" s="9" t="s">
-        <v>405</v>
+        <v>46198</v>
+      </c>
+      <c r="I204" s="12" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="205" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
-        <v>9032163034</v>
+        <v>7673989096</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C205" s="1">
-        <v>1016</v>
+        <v>516</v>
       </c>
       <c r="E205" s="2"/>
       <c r="G205" s="1">
-        <v>2883</v>
+        <v>2368</v>
       </c>
       <c r="H205" s="7">
-        <v>46187</v>
+        <v>46198</v>
       </c>
       <c r="I205" s="9" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
     </row>
     <row r="206" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
-        <v>8142938181</v>
+        <v>9866568921</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="C206" s="1">
-        <v>516</v>
+        <v>50000</v>
       </c>
       <c r="E206" s="2"/>
       <c r="G206" s="1">
-        <v>2882</v>
+        <v>2390</v>
       </c>
       <c r="H206" s="7">
-        <v>46187</v>
-      </c>
-      <c r="I206" s="9" t="s">
-        <v>407</v>
+        <v>46198</v>
+      </c>
+      <c r="I206" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="207" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
-        <v>9000249197</v>
+        <v>9000166687</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="C207" s="1">
-        <v>1116</v>
+        <v>516</v>
       </c>
       <c r="E207" s="2"/>
       <c r="G207" s="1">
-        <v>2879</v>
+        <v>2371</v>
       </c>
       <c r="H207" s="7">
-        <v>46187</v>
-      </c>
-      <c r="I207" s="9" t="s">
-        <v>374</v>
+        <v>46198</v>
+      </c>
+      <c r="I207" s="2" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="208" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
-        <v>7396120056</v>
+        <v>9059454396</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C208" s="1">
-        <v>5000</v>
+        <v>516</v>
       </c>
       <c r="E208" s="2"/>
       <c r="G208" s="1">
-        <v>2878</v>
+        <v>2372</v>
       </c>
       <c r="H208" s="7">
-        <v>46187</v>
-      </c>
-      <c r="I208" s="2" t="s">
-        <v>408</v>
+        <v>46199</v>
+      </c>
+      <c r="I208" s="9" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
-        <v>9618682686</v>
+        <v>9866568921</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="C209" s="1">
-        <v>516</v>
+        <v>50000</v>
       </c>
       <c r="E209" s="2"/>
       <c r="G209" s="1">
-        <v>2889</v>
+        <v>2391</v>
       </c>
       <c r="H209" s="7">
-        <v>46187</v>
-      </c>
-      <c r="I209" s="2"/>
+        <v>46200</v>
+      </c>
+      <c r="I209" s="2" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="210" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="1">
-        <v>9618961007</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C210" s="1">
-        <v>516</v>
-      </c>
+      <c r="A210" s="2"/>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
       <c r="E210" s="2"/>
-      <c r="G210" s="1">
-        <v>2892</v>
-      </c>
-      <c r="H210" s="7">
-        <v>46188</v>
-      </c>
-      <c r="I210" s="9" t="s">
-        <v>409</v>
-      </c>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+      <c r="I210" s="2"/>
     </row>
     <row r="211" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A211" s="1">
-        <v>9951719178</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C211" s="1">
-        <v>516</v>
-      </c>
+      <c r="A211" s="2"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
       <c r="E211" s="2"/>
-      <c r="G211" s="1">
-        <v>2891</v>
-      </c>
-      <c r="H211" s="7">
-        <v>46188</v>
-      </c>
-      <c r="I211" s="9" t="s">
-        <v>410</v>
-      </c>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+      <c r="I211" s="2"/>
     </row>
     <row r="212" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="1">
-        <v>7661854477</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C212" s="1">
-        <v>516</v>
-      </c>
+      <c r="A212" s="2"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
       <c r="E212" s="2"/>
-      <c r="G212" s="1">
-        <v>2890</v>
-      </c>
-      <c r="H212" s="7">
-        <v>46188</v>
-      </c>
-      <c r="I212" s="2" t="s">
-        <v>411</v>
-      </c>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
     </row>
     <row r="213" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A213" s="1">
-        <v>7396120056</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C213" s="1">
-        <v>500</v>
-      </c>
+      <c r="A213" s="2"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
       <c r="E213" s="2"/>
-      <c r="G213" s="1">
-        <v>2899</v>
-      </c>
-      <c r="H213" s="7">
-        <v>46189</v>
-      </c>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
       <c r="I213" s="2"/>
     </row>
     <row r="214" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A214" s="1">
-        <v>9989615167</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C214" s="1">
-        <v>516</v>
-      </c>
+      <c r="A214" s="2"/>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
       <c r="E214" s="2"/>
-      <c r="G214" s="1">
-        <v>2896</v>
-      </c>
-      <c r="H214" s="7">
-        <v>46190</v>
-      </c>
-      <c r="I214" s="2" t="s">
-        <v>412</v>
-      </c>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
     </row>
     <row r="215" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A215" s="1">
-        <v>9700685055</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C215" s="1">
-        <v>516</v>
-      </c>
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
       <c r="E215" s="2"/>
-      <c r="G215" s="1">
-        <v>2355</v>
-      </c>
-      <c r="H215" s="7">
-        <v>46193</v>
-      </c>
-      <c r="I215" s="9" t="s">
-        <v>413</v>
-      </c>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
     </row>
     <row r="216" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A216" s="1">
-        <v>9493936707</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C216" s="1">
-        <v>1632</v>
-      </c>
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
       <c r="E216" s="2"/>
-      <c r="G216" s="1">
-        <v>2354</v>
-      </c>
-      <c r="H216" s="7">
-        <v>46193</v>
-      </c>
-      <c r="I216" s="9" t="s">
-        <v>414</v>
-      </c>
+      <c r="G216" s="2"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
     </row>
     <row r="217" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A217" s="1">
-        <v>9866392184</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C217" s="1">
-        <v>516</v>
-      </c>
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
       <c r="E217" s="2"/>
-      <c r="G217" s="1">
-        <v>2353</v>
-      </c>
-      <c r="H217" s="7">
-        <v>46193</v>
-      </c>
-      <c r="I217" s="9" t="s">
-        <v>415</v>
-      </c>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
     </row>
     <row r="218" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="1">
-        <v>7893998695</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C218" s="1">
-        <v>516</v>
-      </c>
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
       <c r="E218" s="2"/>
-      <c r="G218" s="1">
-        <v>2359</v>
-      </c>
-      <c r="H218" s="7">
-        <v>46194</v>
-      </c>
-      <c r="I218" s="9" t="s">
-        <v>416</v>
-      </c>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
     </row>
     <row r="219" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="1">
-        <v>7893998695</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C219" s="1">
-        <v>1116</v>
-      </c>
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
       <c r="E219" s="2"/>
-      <c r="G219" s="1">
-        <v>2358</v>
-      </c>
-      <c r="H219" s="7">
-        <v>46194</v>
-      </c>
-      <c r="I219" s="9" t="s">
-        <v>416</v>
-      </c>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
     </row>
     <row r="220" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="1">
-        <v>9652489430</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C220" s="1">
-        <v>516</v>
-      </c>
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
       <c r="E220" s="2"/>
-      <c r="G220" s="1">
-        <v>2357</v>
-      </c>
-      <c r="H220" s="7">
-        <v>46194</v>
-      </c>
-      <c r="I220" s="9" t="s">
-        <v>417</v>
-      </c>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
     </row>
     <row r="221" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="1">
-        <v>7780487639</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C221" s="1">
-        <v>516</v>
-      </c>
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
       <c r="E221" s="2"/>
-      <c r="G221" s="1">
-        <v>2361</v>
-      </c>
-      <c r="H221" s="7">
-        <v>46195</v>
-      </c>
-      <c r="I221" s="9" t="s">
-        <v>418</v>
-      </c>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
     </row>
     <row r="222" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="1">
-        <v>9949034545</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C222" s="1">
-        <v>1116</v>
-      </c>
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
       <c r="E222" s="2"/>
-      <c r="G222" s="1">
-        <v>2360</v>
-      </c>
-      <c r="H222" s="7">
-        <v>46195</v>
-      </c>
-      <c r="I222" s="9" t="s">
-        <v>419</v>
-      </c>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
     </row>
     <row r="223" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="1">
-        <v>8341587969</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C223" s="1">
-        <v>1016</v>
-      </c>
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
       <c r="E223" s="2"/>
-      <c r="G223" s="1">
-        <v>2364</v>
-      </c>
-      <c r="H223" s="7">
-        <v>46196</v>
-      </c>
-      <c r="I223" s="10" t="s">
-        <v>420</v>
-      </c>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
     </row>
     <row r="224" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="4">
-        <v>6281659358</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C224" s="1">
-        <v>516</v>
-      </c>
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
       <c r="E224" s="2"/>
-      <c r="G224" s="1">
-        <v>2365</v>
-      </c>
-      <c r="H224" s="7">
-        <v>46197</v>
-      </c>
-      <c r="I224" s="11" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" ht="28.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="1">
-        <v>9440086356</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C225" s="1">
-        <v>501</v>
-      </c>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+    </row>
+    <row r="225" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A225" s="2"/>
+      <c r="B225" s="2"/>
+      <c r="C225" s="2"/>
       <c r="E225" s="2"/>
-      <c r="G225" s="1">
-        <v>2369</v>
-      </c>
-      <c r="H225" s="7">
-        <v>46198</v>
-      </c>
-      <c r="I225" s="12" t="s">
-        <v>422</v>
-      </c>
+      <c r="G225" s="2"/>
+      <c r="H225" s="2"/>
+      <c r="I225" s="2"/>
     </row>
     <row r="226" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="1">
-        <v>7673989096</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C226" s="1">
-        <v>516</v>
-      </c>
+      <c r="A226" s="2"/>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
       <c r="E226" s="2"/>
-      <c r="G226" s="1">
-        <v>2368</v>
-      </c>
-      <c r="H226" s="7">
-        <v>46198</v>
-      </c>
-      <c r="I226" s="9" t="s">
-        <v>423</v>
-      </c>
+      <c r="G226" s="2"/>
+      <c r="H226" s="2"/>
+      <c r="I226" s="2"/>
     </row>
     <row r="227" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A227" s="1">
-        <v>9866568921</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C227" s="1">
-        <v>50000</v>
-      </c>
+      <c r="A227" s="2"/>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
       <c r="E227" s="2"/>
-      <c r="G227" s="1">
-        <v>2390</v>
-      </c>
-      <c r="H227" s="7">
-        <v>46198</v>
-      </c>
-      <c r="I227" s="2" t="s">
-        <v>387</v>
-      </c>
+      <c r="G227" s="2"/>
+      <c r="H227" s="2"/>
+      <c r="I227" s="2"/>
     </row>
     <row r="228" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="1">
-        <v>9000166687</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C228" s="1">
-        <v>516</v>
-      </c>
+      <c r="A228" s="2"/>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
       <c r="E228" s="2"/>
-      <c r="G228" s="1">
-        <v>2371</v>
-      </c>
-      <c r="H228" s="7">
-        <v>46198</v>
-      </c>
-      <c r="I228" s="2" t="s">
-        <v>346</v>
-      </c>
+      <c r="G228" s="2"/>
+      <c r="H228" s="2"/>
+      <c r="I228" s="2"/>
     </row>
     <row r="229" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="1">
-        <v>9059454396</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C229" s="1">
-        <v>516</v>
-      </c>
+      <c r="A229" s="2"/>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
       <c r="E229" s="2"/>
-      <c r="G229" s="1">
-        <v>2372</v>
-      </c>
-      <c r="H229" s="7">
-        <v>46199</v>
-      </c>
-      <c r="I229" s="9" t="s">
-        <v>424</v>
-      </c>
+      <c r="G229" s="2"/>
+      <c r="H229" s="2"/>
+      <c r="I229" s="2"/>
     </row>
     <row r="230" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A230" s="1">
-        <v>9866568921</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C230" s="1">
-        <v>50000</v>
-      </c>
+      <c r="A230" s="2"/>
+      <c r="B230" s="2"/>
+      <c r="C230" s="2"/>
       <c r="E230" s="2"/>
-      <c r="G230" s="1">
-        <v>2391</v>
-      </c>
-      <c r="H230" s="7">
-        <v>46200</v>
-      </c>
-      <c r="I230" s="2" t="s">
-        <v>387</v>
-      </c>
+      <c r="G230" s="2"/>
+      <c r="H230" s="2"/>
+      <c r="I230" s="2"/>
     </row>
     <row r="231" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2"/>
@@ -13416,366 +13045,161 @@
       <c r="H979" s="2"/>
       <c r="I979" s="2"/>
     </row>
-    <row r="980" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A980" s="2"/>
-      <c r="B980" s="2"/>
-      <c r="C980" s="2"/>
-      <c r="E980" s="2"/>
-      <c r="G980" s="2"/>
-      <c r="H980" s="2"/>
-      <c r="I980" s="2"/>
-    </row>
-    <row r="981" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A981" s="2"/>
-      <c r="B981" s="2"/>
-      <c r="C981" s="2"/>
-      <c r="E981" s="2"/>
-      <c r="G981" s="2"/>
-      <c r="H981" s="2"/>
-      <c r="I981" s="2"/>
-    </row>
-    <row r="982" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A982" s="2"/>
-      <c r="B982" s="2"/>
-      <c r="C982" s="2"/>
-      <c r="E982" s="2"/>
-      <c r="G982" s="2"/>
-      <c r="H982" s="2"/>
-      <c r="I982" s="2"/>
-    </row>
-    <row r="983" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A983" s="2"/>
-      <c r="B983" s="2"/>
-      <c r="C983" s="2"/>
-      <c r="E983" s="2"/>
-      <c r="G983" s="2"/>
-      <c r="H983" s="2"/>
-      <c r="I983" s="2"/>
-    </row>
-    <row r="984" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A984" s="2"/>
-      <c r="B984" s="2"/>
-      <c r="C984" s="2"/>
-      <c r="E984" s="2"/>
-      <c r="G984" s="2"/>
-      <c r="H984" s="2"/>
-      <c r="I984" s="2"/>
-    </row>
-    <row r="985" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A985" s="2"/>
-      <c r="B985" s="2"/>
-      <c r="C985" s="2"/>
-      <c r="E985" s="2"/>
-      <c r="G985" s="2"/>
-      <c r="H985" s="2"/>
-      <c r="I985" s="2"/>
-    </row>
-    <row r="986" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A986" s="2"/>
-      <c r="B986" s="2"/>
-      <c r="C986" s="2"/>
-      <c r="E986" s="2"/>
-      <c r="G986" s="2"/>
-      <c r="H986" s="2"/>
-      <c r="I986" s="2"/>
-    </row>
-    <row r="987" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A987" s="2"/>
-      <c r="B987" s="2"/>
-      <c r="C987" s="2"/>
-      <c r="E987" s="2"/>
-      <c r="G987" s="2"/>
-      <c r="H987" s="2"/>
-      <c r="I987" s="2"/>
-    </row>
-    <row r="988" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A988" s="2"/>
-      <c r="B988" s="2"/>
-      <c r="C988" s="2"/>
-      <c r="E988" s="2"/>
-      <c r="G988" s="2"/>
-      <c r="H988" s="2"/>
-      <c r="I988" s="2"/>
-    </row>
-    <row r="989" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A989" s="2"/>
-      <c r="B989" s="2"/>
-      <c r="C989" s="2"/>
-      <c r="E989" s="2"/>
-      <c r="G989" s="2"/>
-      <c r="H989" s="2"/>
-      <c r="I989" s="2"/>
-    </row>
-    <row r="990" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A990" s="2"/>
-      <c r="B990" s="2"/>
-      <c r="C990" s="2"/>
-      <c r="E990" s="2"/>
-      <c r="G990" s="2"/>
-      <c r="H990" s="2"/>
-      <c r="I990" s="2"/>
-    </row>
-    <row r="991" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A991" s="2"/>
-      <c r="B991" s="2"/>
-      <c r="C991" s="2"/>
-      <c r="E991" s="2"/>
-      <c r="G991" s="2"/>
-      <c r="H991" s="2"/>
-      <c r="I991" s="2"/>
-    </row>
-    <row r="992" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A992" s="2"/>
-      <c r="B992" s="2"/>
-      <c r="C992" s="2"/>
-      <c r="E992" s="2"/>
-      <c r="G992" s="2"/>
-      <c r="H992" s="2"/>
-      <c r="I992" s="2"/>
-    </row>
-    <row r="993" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A993" s="2"/>
-      <c r="B993" s="2"/>
-      <c r="C993" s="2"/>
-      <c r="E993" s="2"/>
-      <c r="G993" s="2"/>
-      <c r="H993" s="2"/>
-      <c r="I993" s="2"/>
-    </row>
-    <row r="994" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A994" s="2"/>
-      <c r="B994" s="2"/>
-      <c r="C994" s="2"/>
-      <c r="E994" s="2"/>
-      <c r="G994" s="2"/>
-      <c r="H994" s="2"/>
-      <c r="I994" s="2"/>
-    </row>
-    <row r="995" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A995" s="2"/>
-      <c r="B995" s="2"/>
-      <c r="C995" s="2"/>
-      <c r="E995" s="2"/>
-      <c r="G995" s="2"/>
-      <c r="H995" s="2"/>
-      <c r="I995" s="2"/>
-    </row>
-    <row r="996" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A996" s="2"/>
-      <c r="B996" s="2"/>
-      <c r="C996" s="2"/>
-      <c r="E996" s="2"/>
-      <c r="G996" s="2"/>
-      <c r="H996" s="2"/>
-      <c r="I996" s="2"/>
-    </row>
-    <row r="997" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A997" s="2"/>
-      <c r="B997" s="2"/>
-      <c r="C997" s="2"/>
-      <c r="E997" s="2"/>
-      <c r="G997" s="2"/>
-      <c r="H997" s="2"/>
-      <c r="I997" s="2"/>
-    </row>
-    <row r="998" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A998" s="2"/>
-      <c r="B998" s="2"/>
-      <c r="C998" s="2"/>
-      <c r="E998" s="2"/>
-      <c r="G998" s="2"/>
-      <c r="H998" s="2"/>
-      <c r="I998" s="2"/>
-    </row>
-    <row r="999" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A999" s="2"/>
-      <c r="B999" s="2"/>
-      <c r="C999" s="2"/>
-      <c r="E999" s="2"/>
-      <c r="G999" s="2"/>
-      <c r="H999" s="2"/>
-      <c r="I999" s="2"/>
-    </row>
-    <row r="1000" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1000" s="2"/>
-      <c r="B1000" s="2"/>
-      <c r="C1000" s="2"/>
-      <c r="E1000" s="2"/>
-      <c r="G1000" s="2"/>
-      <c r="H1000" s="2"/>
-      <c r="I1000" s="2"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" display="http://h.no/" xr:uid="{6827C794-51BE-4BAA-B644-BF947E85F7AA}"/>
-    <hyperlink ref="I3" r:id="rId2" display="http://h.no/" xr:uid="{D44D419D-05B4-48B1-8C84-5B2EDE1924A1}"/>
-    <hyperlink ref="I5" r:id="rId3" display="http://h.no/" xr:uid="{C03A975E-D494-4718-8B5C-2F59F7898506}"/>
-    <hyperlink ref="I6" r:id="rId4" display="http://h.no/" xr:uid="{C0D43FC5-72AF-4962-8168-0142F8962829}"/>
-    <hyperlink ref="I7" r:id="rId5" display="http://h.no/" xr:uid="{CB6D9F9F-FCBF-4F3D-9733-0BAEEE25E380}"/>
-    <hyperlink ref="I8" r:id="rId6" display="http://h.no/" xr:uid="{173FF4A8-5D4C-4E79-8858-7D6C568A6390}"/>
-    <hyperlink ref="I9" r:id="rId7" display="http://h.no/" xr:uid="{81728696-2132-4400-A443-5A6F700C9872}"/>
-    <hyperlink ref="I11" r:id="rId8" display="http://h.no/" xr:uid="{0CA0D842-989A-4918-A0F4-CDDBE441EDEF}"/>
-    <hyperlink ref="I12" r:id="rId9" display="http://h.no/" xr:uid="{F39DE2B4-1357-4BD8-BD1D-A29AAFA98A31}"/>
-    <hyperlink ref="I13" r:id="rId10" display="http://h.no/" xr:uid="{B82A9200-8C3E-4B01-8DF5-AC133B4C62AD}"/>
-    <hyperlink ref="I14" r:id="rId11" display="http://h.no/" xr:uid="{33AF5BE4-6F1D-42C8-8852-A7D77B1FD9EF}"/>
-    <hyperlink ref="I15" r:id="rId12" display="http://h.no/" xr:uid="{9341F82E-3A92-4913-9988-4ADBD8609065}"/>
-    <hyperlink ref="I16" r:id="rId13" display="http://h.no/" xr:uid="{D18F42C7-E30E-473B-9906-4FAAE196D127}"/>
-    <hyperlink ref="I17" r:id="rId14" display="http://h.no/" xr:uid="{881E1429-85CD-4E00-9009-BED250207489}"/>
-    <hyperlink ref="I18" r:id="rId15" display="http://h.no/" xr:uid="{0109E2F5-F91B-446C-BF5E-88ACA315A963}"/>
-    <hyperlink ref="I20" r:id="rId16" display="http://h.no/" xr:uid="{DB15F630-47CA-4797-A820-DAE79E74023D}"/>
-    <hyperlink ref="I23" r:id="rId17" display="http://h.no/" xr:uid="{458A02E7-78CC-428E-B1E2-B8F5BBCDB6F1}"/>
-    <hyperlink ref="I24" r:id="rId18" display="http://h.no/" xr:uid="{51BB03B9-7815-434B-BBEA-9379F6E9FEE6}"/>
-    <hyperlink ref="I25" r:id="rId19" display="http://h.no/" xr:uid="{6D9E26AD-1692-4FB3-9B07-508BF0A41538}"/>
-    <hyperlink ref="I27" r:id="rId20" display="http://h.no/" xr:uid="{0294D29E-6C16-40F0-816B-91DEDAC2F18E}"/>
-    <hyperlink ref="I28" r:id="rId21" display="http://h.no/" xr:uid="{D5D6BEBB-991F-4549-9FC9-E73A76F95139}"/>
-    <hyperlink ref="I29" r:id="rId22" display="http://h.no/" xr:uid="{B06894DE-CDD1-4C82-9C4A-C6AE6FFF8588}"/>
-    <hyperlink ref="I30" r:id="rId23" display="http://h.no/" xr:uid="{FC81A4C3-888B-42AE-9F9C-C66DA640282B}"/>
-    <hyperlink ref="I31" r:id="rId24" display="http://h.no/" xr:uid="{19F1C34F-4B9B-48C6-B1DB-2401C38A77A2}"/>
-    <hyperlink ref="I36" r:id="rId25" display="http://h.no/" xr:uid="{4215AD0B-F880-49A6-BAB3-D96B49016E95}"/>
-    <hyperlink ref="I37" r:id="rId26" display="http://h.no/" xr:uid="{FBE6689A-0B4B-4736-9DDB-4F0821F4F3D2}"/>
-    <hyperlink ref="I38" r:id="rId27" display="http://h.no/" xr:uid="{5E8B9AF3-609D-4C3B-9D8C-DE021C6BB021}"/>
-    <hyperlink ref="I39" r:id="rId28" display="http://h.no/" xr:uid="{53AD36ED-5525-4163-AEA7-66722D18227E}"/>
-    <hyperlink ref="I40" r:id="rId29" display="http://h.no/" xr:uid="{333B3AF5-3E46-4EE9-A055-D3D6F4361390}"/>
-    <hyperlink ref="I41" r:id="rId30" display="http://h.no/" xr:uid="{B8796DA3-0B5F-4445-BEE2-92AB84D2D964}"/>
-    <hyperlink ref="I42" r:id="rId31" display="http://h.no/" xr:uid="{3E780B2A-58BD-4F82-A675-FA7644AED09D}"/>
-    <hyperlink ref="I44" r:id="rId32" display="http://h.no/" xr:uid="{7F1F1BDA-ABF4-4587-A847-385911796406}"/>
-    <hyperlink ref="I45" r:id="rId33" display="http://h.no/" xr:uid="{A70D9C4C-7055-4A27-BFF0-BD7CBD079B92}"/>
-    <hyperlink ref="I46" r:id="rId34" display="http://h.no/" xr:uid="{212C0E5A-FC2F-4F65-AC70-D86833DB3CF1}"/>
-    <hyperlink ref="I47" r:id="rId35" display="http://h.no/" xr:uid="{24EF2741-CC7B-4B37-AB7B-793730C2EA75}"/>
-    <hyperlink ref="I54" r:id="rId36" display="http://h.no/" xr:uid="{97513ECE-9E2A-421F-BC78-DE34D5D6EA26}"/>
-    <hyperlink ref="I55" r:id="rId37" display="http://h.no/" xr:uid="{F43310EA-2462-4DCE-91E7-315E5A8289E2}"/>
-    <hyperlink ref="I57" r:id="rId38" display="http://h.no/" xr:uid="{EF8BA555-B586-4260-8284-AEB30EDDB9D0}"/>
-    <hyperlink ref="I58" r:id="rId39" display="http://h.no/" xr:uid="{EEE657D0-CAAB-4A2B-B0CB-25A44B601C27}"/>
-    <hyperlink ref="I59" r:id="rId40" display="http://h.no/" xr:uid="{4220CB6A-C006-4C4E-9F5A-5FFA546AEAAE}"/>
-    <hyperlink ref="I61" r:id="rId41" display="http://h.no/" xr:uid="{B6B65CD6-7489-456C-AB67-348499DC5956}"/>
-    <hyperlink ref="I63" r:id="rId42" display="http://h.no/" xr:uid="{2ECAD1C3-9201-4FEE-9F95-02A43E7FF14D}"/>
-    <hyperlink ref="I64" r:id="rId43" display="http://h.no/" xr:uid="{E1B0F41A-E93B-4805-A8B8-D63210D75A52}"/>
-    <hyperlink ref="I65" r:id="rId44" display="http://h.no/" xr:uid="{DC162C4D-3B55-4055-9F8A-2B7A46190CB2}"/>
-    <hyperlink ref="I66" r:id="rId45" display="http://h.no/" xr:uid="{F108E11E-305D-4F03-95AA-C68B07F47F36}"/>
-    <hyperlink ref="I67" r:id="rId46" display="http://h.no/" xr:uid="{7A55CA21-7702-444E-9377-33257F9F78CB}"/>
-    <hyperlink ref="I68" r:id="rId47" display="http://h.no/" xr:uid="{2F7F971E-D0DE-4495-8647-B9B0796313D7}"/>
-    <hyperlink ref="I70" r:id="rId48" display="http://h.no/" xr:uid="{C2A2AABD-7F6A-423A-8AC6-B72454594B2B}"/>
-    <hyperlink ref="I71" r:id="rId49" display="http://h.no/" xr:uid="{DD1D56C8-36C0-465E-A529-869859F6EA9A}"/>
-    <hyperlink ref="I72" r:id="rId50" display="http://h.no/" xr:uid="{F571B1BC-B3B0-4870-9784-2D0782D2C64F}"/>
-    <hyperlink ref="I73" r:id="rId51" display="http://h.no/" xr:uid="{BAE04688-8179-4961-A940-386D7CF485DF}"/>
-    <hyperlink ref="I74" r:id="rId52" display="http://h.no/" xr:uid="{69A1092D-21C8-4E1C-994D-669D1C4BA7C1}"/>
-    <hyperlink ref="I76" r:id="rId53" display="http://h.no/" xr:uid="{E2671566-78CE-49F8-87ED-EBDD9A6F7982}"/>
-    <hyperlink ref="I77" r:id="rId54" display="http://h.no/" xr:uid="{BA111093-B3CD-43C2-8184-4A4796DE5C46}"/>
-    <hyperlink ref="I78" r:id="rId55" display="http://h.no/" xr:uid="{ACB65C22-E452-47D8-887B-F93B858C92B9}"/>
-    <hyperlink ref="I79" r:id="rId56" display="http://h.no/" xr:uid="{A21A7017-5116-4F0A-A140-3511FC4A937B}"/>
-    <hyperlink ref="I80" r:id="rId57" display="http://h.no/" xr:uid="{B93E5F58-D2A5-4464-8BCA-179687004C78}"/>
-    <hyperlink ref="I81" r:id="rId58" display="http://h.no/" xr:uid="{9FC8F2D1-16A4-435B-BCAE-A7687B2C78E7}"/>
-    <hyperlink ref="I83" r:id="rId59" display="http://h.no/" xr:uid="{F8437F72-F76C-4D47-B147-2F0301EC3555}"/>
-    <hyperlink ref="I84" r:id="rId60" display="http://h.no/" xr:uid="{84609318-46EF-455E-9B2A-A7888467064F}"/>
-    <hyperlink ref="I85" r:id="rId61" display="http://h.no/" xr:uid="{CE5E4683-5F2C-4065-8B54-9516C362BBB7}"/>
-    <hyperlink ref="I86" r:id="rId62" display="http://h.no/" xr:uid="{777B8672-4E60-4358-BC6D-153CB427BF5D}"/>
-    <hyperlink ref="I87" r:id="rId63" display="http://h.no/" xr:uid="{5FD12E0B-1E1E-42CC-B346-122E8A50181F}"/>
-    <hyperlink ref="I88" r:id="rId64" display="http://h.no/" xr:uid="{7E28EABC-8D15-460D-AB26-F64DD6E59F4E}"/>
-    <hyperlink ref="I89" r:id="rId65" display="http://h.no/" xr:uid="{FCBECC4C-652E-4CFC-84A5-F83E53AAC678}"/>
-    <hyperlink ref="I90" r:id="rId66" display="http://h.no/" xr:uid="{81040B66-D256-45A6-846C-C1FBDF93DE45}"/>
-    <hyperlink ref="I91" r:id="rId67" display="http://h.no/" xr:uid="{4ECE62BC-B6BF-429F-99F1-001D11E4B4DA}"/>
-    <hyperlink ref="I93" r:id="rId68" display="http://h.no/" xr:uid="{0C9801D8-6A55-4C59-9CE6-3AC364F27E64}"/>
-    <hyperlink ref="I94" r:id="rId69" display="http://h.no/" xr:uid="{0DF469AD-05F7-447A-92DA-5B7B6D61385F}"/>
-    <hyperlink ref="I95" r:id="rId70" display="http://h.no/" xr:uid="{EFE3F9CF-E60D-4C50-A746-8C67DAED6446}"/>
-    <hyperlink ref="I98" r:id="rId71" display="http://h.no/" xr:uid="{BD3738A3-8694-428A-9147-9BDD16DECFC7}"/>
-    <hyperlink ref="I99" r:id="rId72" display="http://h.no/" xr:uid="{F8836E8F-E16C-4701-9CA5-D8B2C4E67A9D}"/>
-    <hyperlink ref="I100" r:id="rId73" display="http://h.no/" xr:uid="{75BA51F6-B0C2-4645-AF49-51E8C18F227E}"/>
-    <hyperlink ref="I101" r:id="rId74" display="http://h.no/" xr:uid="{53E95D1A-EF1A-4F6B-A85A-696BAD20B1FA}"/>
-    <hyperlink ref="I103" r:id="rId75" display="http://h.no/" xr:uid="{C906D92C-1BFB-4E7D-9E81-B938296A5D0A}"/>
-    <hyperlink ref="I104" r:id="rId76" display="http://h.no/" xr:uid="{F27FB27C-2B71-4AFD-A7E7-9A4291C3CC37}"/>
-    <hyperlink ref="I106" r:id="rId77" display="http://h.no/" xr:uid="{23D6CA5D-59FB-4BFB-8F3C-0FB1A6DEC84B}"/>
-    <hyperlink ref="I107" r:id="rId78" display="http://h.no/" xr:uid="{07275755-E9F9-4A5F-8427-9D99FF614BDE}"/>
-    <hyperlink ref="I108" r:id="rId79" display="http://h.no/" xr:uid="{7E93BCF5-1078-4B6C-A179-69419BE2BDEB}"/>
-    <hyperlink ref="I109" r:id="rId80" display="http://h.no/" xr:uid="{C32C0EB8-B8E5-47D4-9BF7-59E56D7FD07F}"/>
-    <hyperlink ref="I110" r:id="rId81" display="http://h.no/" xr:uid="{522E42F7-D3DF-46F0-9E9E-3CB0A747C645}"/>
-    <hyperlink ref="I111" r:id="rId82" display="http://h.no/" xr:uid="{05833121-E14E-43E1-9614-6DEAB5BD74CF}"/>
-    <hyperlink ref="I112" r:id="rId83" display="http://h.no/" xr:uid="{3373B8F4-0AC0-4C8B-A8C0-0C8AE58C05BA}"/>
-    <hyperlink ref="I113" r:id="rId84" display="http://h.no/" xr:uid="{0D57F428-E4D5-4D6D-89C7-2BBA75791A75}"/>
-    <hyperlink ref="I114" r:id="rId85" display="http://h.no/" xr:uid="{C3B9306E-7366-4A17-8612-53294D099AC8}"/>
-    <hyperlink ref="I116" r:id="rId86" display="http://h.no/" xr:uid="{EFDAA5B1-2CB0-45A1-97F8-7AACA3B84650}"/>
-    <hyperlink ref="I117" r:id="rId87" display="http://h.no/" xr:uid="{4BFEFE38-7FBA-4026-9DF4-077CC2CEE83F}"/>
-    <hyperlink ref="I118" r:id="rId88" display="http://h.no/" xr:uid="{A52FFEB5-992B-4F3C-9B36-00F01F4E1B2B}"/>
-    <hyperlink ref="I119" r:id="rId89" display="http://h.no/" xr:uid="{C1FC02A4-581A-4404-B24B-F395F516DA55}"/>
-    <hyperlink ref="I120" r:id="rId90" display="http://h.no/" xr:uid="{C4092CB5-E712-4ABD-AD36-DC56C9FDAAAB}"/>
-    <hyperlink ref="I121" r:id="rId91" display="http://h.no/" xr:uid="{B522CDE7-CF95-4A1E-800E-48596EA6FEDF}"/>
-    <hyperlink ref="I122" r:id="rId92" display="http://h.no/" xr:uid="{AF953E59-2148-4E2E-BF07-9F1E2DB225B0}"/>
-    <hyperlink ref="I123" r:id="rId93" display="http://h.no/" xr:uid="{12ECA9ED-E980-477A-A364-46E4A16E98A5}"/>
-    <hyperlink ref="I124" r:id="rId94" display="http://h.no/" xr:uid="{A095897E-DAF5-4F83-8D0C-94E40F72D572}"/>
-    <hyperlink ref="I125" r:id="rId95" display="http://h.no/" xr:uid="{A3716CBA-C604-461B-8781-655358773ABD}"/>
-    <hyperlink ref="I127" r:id="rId96" display="http://h.no/" xr:uid="{EB852E77-DEA8-4FDB-BC4D-9983CC6A65B0}"/>
-    <hyperlink ref="I128" r:id="rId97" display="http://h.no/" xr:uid="{B4F37458-6018-422F-B0D8-CDA10FAA0289}"/>
-    <hyperlink ref="I130" r:id="rId98" display="http://h.no/" xr:uid="{F3891D4A-EE62-4F95-B5D6-71AFA438DB89}"/>
-    <hyperlink ref="I131" r:id="rId99" display="http://h.no/" xr:uid="{4EFECB35-C226-4622-A7BE-B428EBE3407A}"/>
-    <hyperlink ref="I133" r:id="rId100" display="http://h.no/" xr:uid="{CEAB65FA-DE06-4C66-A05A-5F225F541327}"/>
-    <hyperlink ref="I134" r:id="rId101" display="http://h.no/" xr:uid="{B9B5BF8A-4662-48B7-8EC7-EF9DBE43051B}"/>
-    <hyperlink ref="I135" r:id="rId102" display="http://h.no/" xr:uid="{81B409D8-E02E-4536-B94B-3D04FFFC6F51}"/>
-    <hyperlink ref="I136" r:id="rId103" display="http://h.no/" xr:uid="{324AE8AF-084C-45F7-BA68-22A42311B5A4}"/>
-    <hyperlink ref="I138" r:id="rId104" display="http://h.no/" xr:uid="{1BC464E2-BD92-41EA-A7A5-9FA7B040ACC9}"/>
-    <hyperlink ref="I140" r:id="rId105" display="http://h.no/" xr:uid="{8B4890A3-C97C-42F4-9986-10310EF52A14}"/>
-    <hyperlink ref="I142" r:id="rId106" display="http://h.no/" xr:uid="{4B38106D-D70B-49C4-9603-B62DACCCCAC3}"/>
-    <hyperlink ref="I143" r:id="rId107" display="http://h.no/" xr:uid="{016BDFE0-61BE-478E-9B8E-5A18C0CA01A9}"/>
-    <hyperlink ref="I144" r:id="rId108" display="http://h.no/" xr:uid="{8E948C07-9415-4B52-BDD2-15D2CDDCA3E0}"/>
-    <hyperlink ref="I146" r:id="rId109" display="http://h.no/" xr:uid="{88940AF7-5A3A-4DED-AC1E-25AF980C0BCF}"/>
-    <hyperlink ref="I147" r:id="rId110" display="http://h.no/" xr:uid="{0515A7F7-FB89-4569-8A08-7A1E2BAD07C8}"/>
-    <hyperlink ref="I148" r:id="rId111" display="http://h.no/" xr:uid="{08828BFE-BD6A-45E1-B7A3-96D112745024}"/>
-    <hyperlink ref="I149" r:id="rId112" display="http://h.no/" xr:uid="{A3EAACFB-5679-4B38-8205-8515487F7BE6}"/>
-    <hyperlink ref="I150" r:id="rId113" display="http://h.no/" xr:uid="{B774E619-C190-44F0-9830-69F4092037EF}"/>
-    <hyperlink ref="I151" r:id="rId114" display="http://h.no/" xr:uid="{7DDA0342-E93A-4B6F-8B4D-FC36EE9544C3}"/>
-    <hyperlink ref="I152" r:id="rId115" display="http://h.no/" xr:uid="{97759399-1458-4E06-9FF9-10710AE09AEB}"/>
-    <hyperlink ref="I154" r:id="rId116" display="http://h.no/" xr:uid="{2FD4CB96-4F6D-4645-95A3-15199708BA44}"/>
-    <hyperlink ref="I155" r:id="rId117" display="http://h.no/" xr:uid="{47309CED-3F05-4491-9116-33737DEE6995}"/>
-    <hyperlink ref="I157" r:id="rId118" display="http://h.no/" xr:uid="{E0A8E1C0-138A-4872-834D-8D25B67E7C38}"/>
-    <hyperlink ref="I160" r:id="rId119" display="http://h.no/" xr:uid="{768C6768-1DA3-4046-BF19-AD67305724F3}"/>
-    <hyperlink ref="I161" r:id="rId120" display="http://h.no/" xr:uid="{09F6CD77-7413-4787-9DA9-6C7083677DAE}"/>
-    <hyperlink ref="I162" r:id="rId121" display="http://h.no/" xr:uid="{83051675-F9C7-4633-9778-5B3C04800C84}"/>
-    <hyperlink ref="I164" r:id="rId122" display="http://h.no/" xr:uid="{46098748-4717-4897-989C-F14B7B411F3D}"/>
-    <hyperlink ref="I165" r:id="rId123" display="http://h.no/" xr:uid="{6C60E2F1-030A-4B99-889E-E9F491A87933}"/>
-    <hyperlink ref="I166" r:id="rId124" display="http://h.no/" xr:uid="{76F37E5A-903D-4CDD-9AD7-B994A4A625FD}"/>
-    <hyperlink ref="I168" r:id="rId125" display="http://h.no/" xr:uid="{1F79BC1C-339B-425E-9805-53612F5CECF8}"/>
-    <hyperlink ref="I169" r:id="rId126" display="http://h.no/" xr:uid="{DCD6B1AF-63FD-4084-86D1-1D5D3AAA3A11}"/>
-    <hyperlink ref="I171" r:id="rId127" display="http://h.no/" xr:uid="{6D9843D4-1627-4766-AE73-B19D6776DEF8}"/>
-    <hyperlink ref="I172" r:id="rId128" display="http://h.no/" xr:uid="{E3DF5309-9761-4C5D-A908-5B67A4BF0241}"/>
-    <hyperlink ref="I173" r:id="rId129" display="http://h.no/" xr:uid="{EF02ECD3-B9F1-41A3-A352-6497230D20B6}"/>
-    <hyperlink ref="I174" r:id="rId130" display="http://h.no/" xr:uid="{62F51D47-3D47-4413-84E1-D503C0C43F74}"/>
-    <hyperlink ref="I175" r:id="rId131" display="http://h.no/" xr:uid="{9DCEDDD3-FC6B-464F-908F-45E877EEA381}"/>
-    <hyperlink ref="I176" r:id="rId132" display="http://h.no/" xr:uid="{66459463-1503-46CC-993A-92976C398E2E}"/>
-    <hyperlink ref="I178" r:id="rId133" display="http://h.no/" xr:uid="{9E9B9F83-3E4C-4BA6-B8AC-D2FAB393A398}"/>
-    <hyperlink ref="I179" r:id="rId134" display="http://h.no/" xr:uid="{DDAB9113-DDCB-45E5-8DEF-F2A3227E2A2B}"/>
-    <hyperlink ref="I182" r:id="rId135" display="http://h.no/" xr:uid="{95AE4F3D-DBA0-4BD1-A484-3A5C2842C3EA}"/>
-    <hyperlink ref="I183" r:id="rId136" display="http://h.no/" xr:uid="{C75AD833-2386-4DBD-9EEE-1B126E9A00CA}"/>
-    <hyperlink ref="I184" r:id="rId137" display="http://h.no/" xr:uid="{C366EBDD-AB8F-4317-946E-AEADA4A6B8A9}"/>
-    <hyperlink ref="I186" r:id="rId138" display="http://h.no/" xr:uid="{1BCB51F9-D916-4823-A606-A246B0560A8E}"/>
-    <hyperlink ref="I188" r:id="rId139" display="http://h.no/" xr:uid="{F67019C8-E4E6-43AB-9CC7-F4EAD8E6D7A8}"/>
-    <hyperlink ref="I189" r:id="rId140" display="http://h.no/" xr:uid="{0931210E-E95E-4741-9C81-F4D7AE01942F}"/>
-    <hyperlink ref="I191" r:id="rId141" display="http://h.no/" xr:uid="{7F913949-5DBA-4A26-9378-49D5A6E2D6A5}"/>
-    <hyperlink ref="I192" r:id="rId142" display="http://h.no/" xr:uid="{FCA0BEDD-421E-4463-AE18-FF84A88A272F}"/>
-    <hyperlink ref="I193" r:id="rId143" display="http://h.no/" xr:uid="{4D787112-C3F9-4DF3-9CB0-0C8A36DCAAAD}"/>
-    <hyperlink ref="I194" r:id="rId144" display="http://h.no/" xr:uid="{5E9AE4A5-36FF-4230-9B54-5F0B6BEE55D0}"/>
-    <hyperlink ref="I195" r:id="rId145" display="http://h.no/" xr:uid="{3340FF53-EA79-4332-A5BD-9DE6331E9AB7}"/>
-    <hyperlink ref="I196" r:id="rId146" display="http://h.no/" xr:uid="{D26C0BE5-33C3-40D7-AAFF-91D706D0E057}"/>
-    <hyperlink ref="I198" r:id="rId147" display="http://h.no/" xr:uid="{24B96048-0523-4702-A082-D66A8385A179}"/>
-    <hyperlink ref="I199" r:id="rId148" display="http://h.no/" xr:uid="{7FA6FC02-E97F-4FD8-9C97-F69E501C085A}"/>
-    <hyperlink ref="I200" r:id="rId149" display="http://h.no/" xr:uid="{C89DEF5E-F4A6-456A-B4B1-0542EA87E101}"/>
-    <hyperlink ref="I201" r:id="rId150" display="http://h.no/" xr:uid="{8F467F7F-DB59-4D36-99E6-2A49551A73CD}"/>
-    <hyperlink ref="I203" r:id="rId151" display="http://h.no/" xr:uid="{A6954079-51B0-4190-9711-D2AC6C91FAE8}"/>
-    <hyperlink ref="I204" r:id="rId152" display="http://h.no/" xr:uid="{A52C60D4-D58F-4DE7-A75D-BE04DF970138}"/>
-    <hyperlink ref="I205" r:id="rId153" display="http://h.no/" xr:uid="{223D06D1-DB5F-477F-B2CF-29AF315EE8CE}"/>
-    <hyperlink ref="I206" r:id="rId154" display="http://h.no/" xr:uid="{547633B1-2152-4266-A10D-6FF347ECE697}"/>
-    <hyperlink ref="I207" r:id="rId155" display="http://h.no/" xr:uid="{95CB6AC2-71BB-4208-8550-84E407157E37}"/>
-    <hyperlink ref="I210" r:id="rId156" display="http://h.no/" xr:uid="{9C039A35-C968-44CE-B7AC-B3BB2DB9A96E}"/>
-    <hyperlink ref="I211" r:id="rId157" display="http://h.no/" xr:uid="{E4651755-1FAB-4224-913A-9A4B9BE8E068}"/>
-    <hyperlink ref="I215" r:id="rId158" display="http://h.no/" xr:uid="{B9F4F1F9-5EE3-4BD4-8F18-EDDE54978316}"/>
-    <hyperlink ref="I216" r:id="rId159" display="http://h.no/" xr:uid="{C59E32FA-F2D8-4789-B9AB-95825A0348E5}"/>
-    <hyperlink ref="I217" r:id="rId160" display="http://h.no/" xr:uid="{7BCCF3BD-CFF8-432A-9EB7-7C7012F4F3A0}"/>
-    <hyperlink ref="I218" r:id="rId161" display="http://h.no/" xr:uid="{A1DA7A81-1856-46C7-9466-F3FF38568499}"/>
-    <hyperlink ref="I219" r:id="rId162" display="http://h.no/" xr:uid="{1C6A6375-2F5C-4635-91E0-7A7DFAA1DBD4}"/>
-    <hyperlink ref="I220" r:id="rId163" display="http://h.no/" xr:uid="{A655F388-9251-423B-92E6-49D794A37F70}"/>
-    <hyperlink ref="I221" r:id="rId164" display="http://h.no/" xr:uid="{7E482AE4-2672-4277-9A2E-149E91C88C16}"/>
-    <hyperlink ref="I222" r:id="rId165" display="http://h.no/" xr:uid="{C9F53DD3-4BE1-4653-91A4-4D8D4A4188FF}"/>
-    <hyperlink ref="I223" r:id="rId166" display="http://h.no/" xr:uid="{484E5224-ABA1-4B91-ACCB-5F8670F53E8B}"/>
-    <hyperlink ref="I224" r:id="rId167" display="http://h.no/" xr:uid="{B1A0C742-35D2-42ED-910A-605ACCCEB76B}"/>
-    <hyperlink ref="I226" r:id="rId168" display="http://h.no/" xr:uid="{358E8AC6-E8D2-46EA-9E76-357DB44BB0A8}"/>
-    <hyperlink ref="I229" r:id="rId169" display="http://h.no/" xr:uid="{11688016-9959-481A-9979-2A42FCE385C5}"/>
+    <hyperlink ref="I2" r:id="rId1" display="http://h.no/" xr:uid="{458A02E7-78CC-428E-B1E2-B8F5BBCDB6F1}"/>
+    <hyperlink ref="I3" r:id="rId2" display="http://h.no/" xr:uid="{51BB03B9-7815-434B-BBEA-9379F6E9FEE6}"/>
+    <hyperlink ref="I4" r:id="rId3" display="http://h.no/" xr:uid="{6D9E26AD-1692-4FB3-9B07-508BF0A41538}"/>
+    <hyperlink ref="I6" r:id="rId4" display="http://h.no/" xr:uid="{0294D29E-6C16-40F0-816B-91DEDAC2F18E}"/>
+    <hyperlink ref="I7" r:id="rId5" display="http://h.no/" xr:uid="{D5D6BEBB-991F-4549-9FC9-E73A76F95139}"/>
+    <hyperlink ref="I8" r:id="rId6" display="http://h.no/" xr:uid="{B06894DE-CDD1-4C82-9C4A-C6AE6FFF8588}"/>
+    <hyperlink ref="I9" r:id="rId7" display="http://h.no/" xr:uid="{FC81A4C3-888B-42AE-9F9C-C66DA640282B}"/>
+    <hyperlink ref="I10" r:id="rId8" display="http://h.no/" xr:uid="{19F1C34F-4B9B-48C6-B1DB-2401C38A77A2}"/>
+    <hyperlink ref="I15" r:id="rId9" display="http://h.no/" xr:uid="{4215AD0B-F880-49A6-BAB3-D96B49016E95}"/>
+    <hyperlink ref="I16" r:id="rId10" display="http://h.no/" xr:uid="{FBE6689A-0B4B-4736-9DDB-4F0821F4F3D2}"/>
+    <hyperlink ref="I17" r:id="rId11" display="http://h.no/" xr:uid="{5E8B9AF3-609D-4C3B-9D8C-DE021C6BB021}"/>
+    <hyperlink ref="I18" r:id="rId12" display="http://h.no/" xr:uid="{53AD36ED-5525-4163-AEA7-66722D18227E}"/>
+    <hyperlink ref="I19" r:id="rId13" display="http://h.no/" xr:uid="{333B3AF5-3E46-4EE9-A055-D3D6F4361390}"/>
+    <hyperlink ref="I20" r:id="rId14" display="http://h.no/" xr:uid="{B8796DA3-0B5F-4445-BEE2-92AB84D2D964}"/>
+    <hyperlink ref="I21" r:id="rId15" display="http://h.no/" xr:uid="{3E780B2A-58BD-4F82-A675-FA7644AED09D}"/>
+    <hyperlink ref="I23" r:id="rId16" display="http://h.no/" xr:uid="{7F1F1BDA-ABF4-4587-A847-385911796406}"/>
+    <hyperlink ref="I24" r:id="rId17" display="http://h.no/" xr:uid="{A70D9C4C-7055-4A27-BFF0-BD7CBD079B92}"/>
+    <hyperlink ref="I25" r:id="rId18" display="http://h.no/" xr:uid="{212C0E5A-FC2F-4F65-AC70-D86833DB3CF1}"/>
+    <hyperlink ref="I26" r:id="rId19" display="http://h.no/" xr:uid="{24EF2741-CC7B-4B37-AB7B-793730C2EA75}"/>
+    <hyperlink ref="I33" r:id="rId20" display="http://h.no/" xr:uid="{97513ECE-9E2A-421F-BC78-DE34D5D6EA26}"/>
+    <hyperlink ref="I34" r:id="rId21" display="http://h.no/" xr:uid="{F43310EA-2462-4DCE-91E7-315E5A8289E2}"/>
+    <hyperlink ref="I36" r:id="rId22" display="http://h.no/" xr:uid="{EF8BA555-B586-4260-8284-AEB30EDDB9D0}"/>
+    <hyperlink ref="I37" r:id="rId23" display="http://h.no/" xr:uid="{EEE657D0-CAAB-4A2B-B0CB-25A44B601C27}"/>
+    <hyperlink ref="I38" r:id="rId24" display="http://h.no/" xr:uid="{4220CB6A-C006-4C4E-9F5A-5FFA546AEAAE}"/>
+    <hyperlink ref="I40" r:id="rId25" display="http://h.no/" xr:uid="{B6B65CD6-7489-456C-AB67-348499DC5956}"/>
+    <hyperlink ref="I42" r:id="rId26" display="http://h.no/" xr:uid="{2ECAD1C3-9201-4FEE-9F95-02A43E7FF14D}"/>
+    <hyperlink ref="I43" r:id="rId27" display="http://h.no/" xr:uid="{E1B0F41A-E93B-4805-A8B8-D63210D75A52}"/>
+    <hyperlink ref="I44" r:id="rId28" display="http://h.no/" xr:uid="{DC162C4D-3B55-4055-9F8A-2B7A46190CB2}"/>
+    <hyperlink ref="I45" r:id="rId29" display="http://h.no/" xr:uid="{F108E11E-305D-4F03-95AA-C68B07F47F36}"/>
+    <hyperlink ref="I46" r:id="rId30" display="http://h.no/" xr:uid="{7A55CA21-7702-444E-9377-33257F9F78CB}"/>
+    <hyperlink ref="I47" r:id="rId31" display="http://h.no/" xr:uid="{2F7F971E-D0DE-4495-8647-B9B0796313D7}"/>
+    <hyperlink ref="I49" r:id="rId32" display="http://h.no/" xr:uid="{C2A2AABD-7F6A-423A-8AC6-B72454594B2B}"/>
+    <hyperlink ref="I50" r:id="rId33" display="http://h.no/" xr:uid="{DD1D56C8-36C0-465E-A529-869859F6EA9A}"/>
+    <hyperlink ref="I51" r:id="rId34" display="http://h.no/" xr:uid="{F571B1BC-B3B0-4870-9784-2D0782D2C64F}"/>
+    <hyperlink ref="I52" r:id="rId35" display="http://h.no/" xr:uid="{BAE04688-8179-4961-A940-386D7CF485DF}"/>
+    <hyperlink ref="I53" r:id="rId36" display="http://h.no/" xr:uid="{69A1092D-21C8-4E1C-994D-669D1C4BA7C1}"/>
+    <hyperlink ref="I55" r:id="rId37" display="http://h.no/" xr:uid="{E2671566-78CE-49F8-87ED-EBDD9A6F7982}"/>
+    <hyperlink ref="I56" r:id="rId38" display="http://h.no/" xr:uid="{BA111093-B3CD-43C2-8184-4A4796DE5C46}"/>
+    <hyperlink ref="I57" r:id="rId39" display="http://h.no/" xr:uid="{ACB65C22-E452-47D8-887B-F93B858C92B9}"/>
+    <hyperlink ref="I58" r:id="rId40" display="http://h.no/" xr:uid="{A21A7017-5116-4F0A-A140-3511FC4A937B}"/>
+    <hyperlink ref="I59" r:id="rId41" display="http://h.no/" xr:uid="{B93E5F58-D2A5-4464-8BCA-179687004C78}"/>
+    <hyperlink ref="I60" r:id="rId42" display="http://h.no/" xr:uid="{9FC8F2D1-16A4-435B-BCAE-A7687B2C78E7}"/>
+    <hyperlink ref="I62" r:id="rId43" display="http://h.no/" xr:uid="{F8437F72-F76C-4D47-B147-2F0301EC3555}"/>
+    <hyperlink ref="I63" r:id="rId44" display="http://h.no/" xr:uid="{84609318-46EF-455E-9B2A-A7888467064F}"/>
+    <hyperlink ref="I64" r:id="rId45" display="http://h.no/" xr:uid="{CE5E4683-5F2C-4065-8B54-9516C362BBB7}"/>
+    <hyperlink ref="I65" r:id="rId46" display="http://h.no/" xr:uid="{777B8672-4E60-4358-BC6D-153CB427BF5D}"/>
+    <hyperlink ref="I66" r:id="rId47" display="http://h.no/" xr:uid="{5FD12E0B-1E1E-42CC-B346-122E8A50181F}"/>
+    <hyperlink ref="I67" r:id="rId48" display="http://h.no/" xr:uid="{7E28EABC-8D15-460D-AB26-F64DD6E59F4E}"/>
+    <hyperlink ref="I68" r:id="rId49" display="http://h.no/" xr:uid="{FCBECC4C-652E-4CFC-84A5-F83E53AAC678}"/>
+    <hyperlink ref="I69" r:id="rId50" display="http://h.no/" xr:uid="{81040B66-D256-45A6-846C-C1FBDF93DE45}"/>
+    <hyperlink ref="I70" r:id="rId51" display="http://h.no/" xr:uid="{4ECE62BC-B6BF-429F-99F1-001D11E4B4DA}"/>
+    <hyperlink ref="I72" r:id="rId52" display="http://h.no/" xr:uid="{0C9801D8-6A55-4C59-9CE6-3AC364F27E64}"/>
+    <hyperlink ref="I73" r:id="rId53" display="http://h.no/" xr:uid="{0DF469AD-05F7-447A-92DA-5B7B6D61385F}"/>
+    <hyperlink ref="I74" r:id="rId54" display="http://h.no/" xr:uid="{EFE3F9CF-E60D-4C50-A746-8C67DAED6446}"/>
+    <hyperlink ref="I77" r:id="rId55" display="http://h.no/" xr:uid="{BD3738A3-8694-428A-9147-9BDD16DECFC7}"/>
+    <hyperlink ref="I78" r:id="rId56" display="http://h.no/" xr:uid="{F8836E8F-E16C-4701-9CA5-D8B2C4E67A9D}"/>
+    <hyperlink ref="I79" r:id="rId57" display="http://h.no/" xr:uid="{75BA51F6-B0C2-4645-AF49-51E8C18F227E}"/>
+    <hyperlink ref="I80" r:id="rId58" display="http://h.no/" xr:uid="{53E95D1A-EF1A-4F6B-A85A-696BAD20B1FA}"/>
+    <hyperlink ref="I82" r:id="rId59" display="http://h.no/" xr:uid="{C906D92C-1BFB-4E7D-9E81-B938296A5D0A}"/>
+    <hyperlink ref="I83" r:id="rId60" display="http://h.no/" xr:uid="{F27FB27C-2B71-4AFD-A7E7-9A4291C3CC37}"/>
+    <hyperlink ref="I85" r:id="rId61" display="http://h.no/" xr:uid="{23D6CA5D-59FB-4BFB-8F3C-0FB1A6DEC84B}"/>
+    <hyperlink ref="I86" r:id="rId62" display="http://h.no/" xr:uid="{07275755-E9F9-4A5F-8427-9D99FF614BDE}"/>
+    <hyperlink ref="I87" r:id="rId63" display="http://h.no/" xr:uid="{7E93BCF5-1078-4B6C-A179-69419BE2BDEB}"/>
+    <hyperlink ref="I88" r:id="rId64" display="http://h.no/" xr:uid="{C32C0EB8-B8E5-47D4-9BF7-59E56D7FD07F}"/>
+    <hyperlink ref="I89" r:id="rId65" display="http://h.no/" xr:uid="{522E42F7-D3DF-46F0-9E9E-3CB0A747C645}"/>
+    <hyperlink ref="I90" r:id="rId66" display="http://h.no/" xr:uid="{05833121-E14E-43E1-9614-6DEAB5BD74CF}"/>
+    <hyperlink ref="I91" r:id="rId67" display="http://h.no/" xr:uid="{3373B8F4-0AC0-4C8B-A8C0-0C8AE58C05BA}"/>
+    <hyperlink ref="I92" r:id="rId68" display="http://h.no/" xr:uid="{0D57F428-E4D5-4D6D-89C7-2BBA75791A75}"/>
+    <hyperlink ref="I93" r:id="rId69" display="http://h.no/" xr:uid="{C3B9306E-7366-4A17-8612-53294D099AC8}"/>
+    <hyperlink ref="I95" r:id="rId70" display="http://h.no/" xr:uid="{EFDAA5B1-2CB0-45A1-97F8-7AACA3B84650}"/>
+    <hyperlink ref="I96" r:id="rId71" display="http://h.no/" xr:uid="{4BFEFE38-7FBA-4026-9DF4-077CC2CEE83F}"/>
+    <hyperlink ref="I97" r:id="rId72" display="http://h.no/" xr:uid="{A52FFEB5-992B-4F3C-9B36-00F01F4E1B2B}"/>
+    <hyperlink ref="I98" r:id="rId73" display="http://h.no/" xr:uid="{C1FC02A4-581A-4404-B24B-F395F516DA55}"/>
+    <hyperlink ref="I99" r:id="rId74" display="http://h.no/" xr:uid="{C4092CB5-E712-4ABD-AD36-DC56C9FDAAAB}"/>
+    <hyperlink ref="I100" r:id="rId75" display="http://h.no/" xr:uid="{B522CDE7-CF95-4A1E-800E-48596EA6FEDF}"/>
+    <hyperlink ref="I101" r:id="rId76" display="http://h.no/" xr:uid="{AF953E59-2148-4E2E-BF07-9F1E2DB225B0}"/>
+    <hyperlink ref="I102" r:id="rId77" display="http://h.no/" xr:uid="{12ECA9ED-E980-477A-A364-46E4A16E98A5}"/>
+    <hyperlink ref="I103" r:id="rId78" display="http://h.no/" xr:uid="{A095897E-DAF5-4F83-8D0C-94E40F72D572}"/>
+    <hyperlink ref="I104" r:id="rId79" display="http://h.no/" xr:uid="{A3716CBA-C604-461B-8781-655358773ABD}"/>
+    <hyperlink ref="I106" r:id="rId80" display="http://h.no/" xr:uid="{EB852E77-DEA8-4FDB-BC4D-9983CC6A65B0}"/>
+    <hyperlink ref="I107" r:id="rId81" display="http://h.no/" xr:uid="{B4F37458-6018-422F-B0D8-CDA10FAA0289}"/>
+    <hyperlink ref="I109" r:id="rId82" display="http://h.no/" xr:uid="{F3891D4A-EE62-4F95-B5D6-71AFA438DB89}"/>
+    <hyperlink ref="I110" r:id="rId83" display="http://h.no/" xr:uid="{4EFECB35-C226-4622-A7BE-B428EBE3407A}"/>
+    <hyperlink ref="I112" r:id="rId84" display="http://h.no/" xr:uid="{CEAB65FA-DE06-4C66-A05A-5F225F541327}"/>
+    <hyperlink ref="I113" r:id="rId85" display="http://h.no/" xr:uid="{B9B5BF8A-4662-48B7-8EC7-EF9DBE43051B}"/>
+    <hyperlink ref="I114" r:id="rId86" display="http://h.no/" xr:uid="{81B409D8-E02E-4536-B94B-3D04FFFC6F51}"/>
+    <hyperlink ref="I115" r:id="rId87" display="http://h.no/" xr:uid="{324AE8AF-084C-45F7-BA68-22A42311B5A4}"/>
+    <hyperlink ref="I117" r:id="rId88" display="http://h.no/" xr:uid="{1BC464E2-BD92-41EA-A7A5-9FA7B040ACC9}"/>
+    <hyperlink ref="I119" r:id="rId89" display="http://h.no/" xr:uid="{8B4890A3-C97C-42F4-9986-10310EF52A14}"/>
+    <hyperlink ref="I121" r:id="rId90" display="http://h.no/" xr:uid="{4B38106D-D70B-49C4-9603-B62DACCCCAC3}"/>
+    <hyperlink ref="I122" r:id="rId91" display="http://h.no/" xr:uid="{016BDFE0-61BE-478E-9B8E-5A18C0CA01A9}"/>
+    <hyperlink ref="I123" r:id="rId92" display="http://h.no/" xr:uid="{8E948C07-9415-4B52-BDD2-15D2CDDCA3E0}"/>
+    <hyperlink ref="I125" r:id="rId93" display="http://h.no/" xr:uid="{88940AF7-5A3A-4DED-AC1E-25AF980C0BCF}"/>
+    <hyperlink ref="I126" r:id="rId94" display="http://h.no/" xr:uid="{0515A7F7-FB89-4569-8A08-7A1E2BAD07C8}"/>
+    <hyperlink ref="I127" r:id="rId95" display="http://h.no/" xr:uid="{08828BFE-BD6A-45E1-B7A3-96D112745024}"/>
+    <hyperlink ref="I128" r:id="rId96" display="http://h.no/" xr:uid="{A3EAACFB-5679-4B38-8205-8515487F7BE6}"/>
+    <hyperlink ref="I129" r:id="rId97" display="http://h.no/" xr:uid="{B774E619-C190-44F0-9830-69F4092037EF}"/>
+    <hyperlink ref="I130" r:id="rId98" display="http://h.no/" xr:uid="{7DDA0342-E93A-4B6F-8B4D-FC36EE9544C3}"/>
+    <hyperlink ref="I131" r:id="rId99" display="http://h.no/" xr:uid="{97759399-1458-4E06-9FF9-10710AE09AEB}"/>
+    <hyperlink ref="I133" r:id="rId100" display="http://h.no/" xr:uid="{2FD4CB96-4F6D-4645-95A3-15199708BA44}"/>
+    <hyperlink ref="I134" r:id="rId101" display="http://h.no/" xr:uid="{47309CED-3F05-4491-9116-33737DEE6995}"/>
+    <hyperlink ref="I136" r:id="rId102" display="http://h.no/" xr:uid="{E0A8E1C0-138A-4872-834D-8D25B67E7C38}"/>
+    <hyperlink ref="I139" r:id="rId103" display="http://h.no/" xr:uid="{768C6768-1DA3-4046-BF19-AD67305724F3}"/>
+    <hyperlink ref="I140" r:id="rId104" display="http://h.no/" xr:uid="{09F6CD77-7413-4787-9DA9-6C7083677DAE}"/>
+    <hyperlink ref="I141" r:id="rId105" display="http://h.no/" xr:uid="{83051675-F9C7-4633-9778-5B3C04800C84}"/>
+    <hyperlink ref="I143" r:id="rId106" display="http://h.no/" xr:uid="{46098748-4717-4897-989C-F14B7B411F3D}"/>
+    <hyperlink ref="I144" r:id="rId107" display="http://h.no/" xr:uid="{6C60E2F1-030A-4B99-889E-E9F491A87933}"/>
+    <hyperlink ref="I145" r:id="rId108" display="http://h.no/" xr:uid="{76F37E5A-903D-4CDD-9AD7-B994A4A625FD}"/>
+    <hyperlink ref="I147" r:id="rId109" display="http://h.no/" xr:uid="{1F79BC1C-339B-425E-9805-53612F5CECF8}"/>
+    <hyperlink ref="I148" r:id="rId110" display="http://h.no/" xr:uid="{DCD6B1AF-63FD-4084-86D1-1D5D3AAA3A11}"/>
+    <hyperlink ref="I150" r:id="rId111" display="http://h.no/" xr:uid="{6D9843D4-1627-4766-AE73-B19D6776DEF8}"/>
+    <hyperlink ref="I151" r:id="rId112" display="http://h.no/" xr:uid="{E3DF5309-9761-4C5D-A908-5B67A4BF0241}"/>
+    <hyperlink ref="I152" r:id="rId113" display="http://h.no/" xr:uid="{EF02ECD3-B9F1-41A3-A352-6497230D20B6}"/>
+    <hyperlink ref="I153" r:id="rId114" display="http://h.no/" xr:uid="{62F51D47-3D47-4413-84E1-D503C0C43F74}"/>
+    <hyperlink ref="I154" r:id="rId115" display="http://h.no/" xr:uid="{9DCEDDD3-FC6B-464F-908F-45E877EEA381}"/>
+    <hyperlink ref="I155" r:id="rId116" display="http://h.no/" xr:uid="{66459463-1503-46CC-993A-92976C398E2E}"/>
+    <hyperlink ref="I157" r:id="rId117" display="http://h.no/" xr:uid="{9E9B9F83-3E4C-4BA6-B8AC-D2FAB393A398}"/>
+    <hyperlink ref="I158" r:id="rId118" display="http://h.no/" xr:uid="{DDAB9113-DDCB-45E5-8DEF-F2A3227E2A2B}"/>
+    <hyperlink ref="I161" r:id="rId119" display="http://h.no/" xr:uid="{95AE4F3D-DBA0-4BD1-A484-3A5C2842C3EA}"/>
+    <hyperlink ref="I162" r:id="rId120" display="http://h.no/" xr:uid="{C75AD833-2386-4DBD-9EEE-1B126E9A00CA}"/>
+    <hyperlink ref="I163" r:id="rId121" display="http://h.no/" xr:uid="{C366EBDD-AB8F-4317-946E-AEADA4A6B8A9}"/>
+    <hyperlink ref="I165" r:id="rId122" display="http://h.no/" xr:uid="{1BCB51F9-D916-4823-A606-A246B0560A8E}"/>
+    <hyperlink ref="I167" r:id="rId123" display="http://h.no/" xr:uid="{F67019C8-E4E6-43AB-9CC7-F4EAD8E6D7A8}"/>
+    <hyperlink ref="I168" r:id="rId124" display="http://h.no/" xr:uid="{0931210E-E95E-4741-9C81-F4D7AE01942F}"/>
+    <hyperlink ref="I170" r:id="rId125" display="http://h.no/" xr:uid="{7F913949-5DBA-4A26-9378-49D5A6E2D6A5}"/>
+    <hyperlink ref="I171" r:id="rId126" display="http://h.no/" xr:uid="{FCA0BEDD-421E-4463-AE18-FF84A88A272F}"/>
+    <hyperlink ref="I172" r:id="rId127" display="http://h.no/" xr:uid="{4D787112-C3F9-4DF3-9CB0-0C8A36DCAAAD}"/>
+    <hyperlink ref="I173" r:id="rId128" display="http://h.no/" xr:uid="{5E9AE4A5-36FF-4230-9B54-5F0B6BEE55D0}"/>
+    <hyperlink ref="I174" r:id="rId129" display="http://h.no/" xr:uid="{3340FF53-EA79-4332-A5BD-9DE6331E9AB7}"/>
+    <hyperlink ref="I175" r:id="rId130" display="http://h.no/" xr:uid="{D26C0BE5-33C3-40D7-AAFF-91D706D0E057}"/>
+    <hyperlink ref="I177" r:id="rId131" display="http://h.no/" xr:uid="{24B96048-0523-4702-A082-D66A8385A179}"/>
+    <hyperlink ref="I178" r:id="rId132" display="http://h.no/" xr:uid="{7FA6FC02-E97F-4FD8-9C97-F69E501C085A}"/>
+    <hyperlink ref="I179" r:id="rId133" display="http://h.no/" xr:uid="{C89DEF5E-F4A6-456A-B4B1-0542EA87E101}"/>
+    <hyperlink ref="I180" r:id="rId134" display="http://h.no/" xr:uid="{8F467F7F-DB59-4D36-99E6-2A49551A73CD}"/>
+    <hyperlink ref="I182" r:id="rId135" display="http://h.no/" xr:uid="{A6954079-51B0-4190-9711-D2AC6C91FAE8}"/>
+    <hyperlink ref="I183" r:id="rId136" display="http://h.no/" xr:uid="{A52C60D4-D58F-4DE7-A75D-BE04DF970138}"/>
+    <hyperlink ref="I184" r:id="rId137" display="http://h.no/" xr:uid="{223D06D1-DB5F-477F-B2CF-29AF315EE8CE}"/>
+    <hyperlink ref="I185" r:id="rId138" display="http://h.no/" xr:uid="{547633B1-2152-4266-A10D-6FF347ECE697}"/>
+    <hyperlink ref="I186" r:id="rId139" display="http://h.no/" xr:uid="{95CB6AC2-71BB-4208-8550-84E407157E37}"/>
+    <hyperlink ref="I189" r:id="rId140" display="http://h.no/" xr:uid="{9C039A35-C968-44CE-B7AC-B3BB2DB9A96E}"/>
+    <hyperlink ref="I190" r:id="rId141" display="http://h.no/" xr:uid="{E4651755-1FAB-4224-913A-9A4B9BE8E068}"/>
+    <hyperlink ref="I194" r:id="rId142" display="http://h.no/" xr:uid="{B9F4F1F9-5EE3-4BD4-8F18-EDDE54978316}"/>
+    <hyperlink ref="I195" r:id="rId143" display="http://h.no/" xr:uid="{C59E32FA-F2D8-4789-B9AB-95825A0348E5}"/>
+    <hyperlink ref="I196" r:id="rId144" display="http://h.no/" xr:uid="{7BCCF3BD-CFF8-432A-9EB7-7C7012F4F3A0}"/>
+    <hyperlink ref="I197" r:id="rId145" display="http://h.no/" xr:uid="{A1DA7A81-1856-46C7-9466-F3FF38568499}"/>
+    <hyperlink ref="I198" r:id="rId146" display="http://h.no/" xr:uid="{1C6A6375-2F5C-4635-91E0-7A7DFAA1DBD4}"/>
+    <hyperlink ref="I199" r:id="rId147" display="http://h.no/" xr:uid="{A655F388-9251-423B-92E6-49D794A37F70}"/>
+    <hyperlink ref="I200" r:id="rId148" display="http://h.no/" xr:uid="{7E482AE4-2672-4277-9A2E-149E91C88C16}"/>
+    <hyperlink ref="I201" r:id="rId149" display="http://h.no/" xr:uid="{C9F53DD3-4BE1-4653-91A4-4D8D4A4188FF}"/>
+    <hyperlink ref="I202" r:id="rId150" display="http://h.no/" xr:uid="{484E5224-ABA1-4B91-ACCB-5F8670F53E8B}"/>
+    <hyperlink ref="I203" r:id="rId151" display="http://h.no/" xr:uid="{B1A0C742-35D2-42ED-910A-605ACCCEB76B}"/>
+    <hyperlink ref="I205" r:id="rId152" display="http://h.no/" xr:uid="{358E8AC6-E8D2-46EA-9E76-357DB44BB0A8}"/>
+    <hyperlink ref="I208" r:id="rId153" display="http://h.no/" xr:uid="{11688016-9959-481A-9979-2A42FCE385C5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
